--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
         <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
         <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
         <v>2.84</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I6" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>2.6</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X2" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL2" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.96</v>
+        <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1610,31 +1610,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.86</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1859,33 +1859,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="G6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.54</v>
-      </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>4.4</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,261 +2096,515 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:27:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hafnarfjordur</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Stjarnan</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.07</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q8" t="n">
         <v>1.01</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-07-01 07:18:53</t>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,16 +866,16 @@
         <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J2" t="n">
         <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -899,7 +899,7 @@
         <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="U2" t="n">
         <v>2.7</v>
@@ -917,10 +917,10 @@
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
         <v>20</v>
@@ -932,7 +932,7 @@
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
         <v>25</v>
@@ -947,13 +947,13 @@
         <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
         <v>60</v>
@@ -965,19 +965,19 @@
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
         <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
         <v>8.800000000000001</v>
@@ -989,10 +989,10 @@
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>10.5</v>
@@ -1001,19 +1001,19 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD2" t="n">
         <v>20</v>
       </c>
       <c r="BE2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1022,72 +1022,72 @@
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
         <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
         <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>36</v>
       </c>
       <c r="BY2" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,28 +1356,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,31 +1610,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.44</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2113,33 +2113,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,261 +2350,515 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:35:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Hafnarfjordur</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Stjarnan</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-07-01 09:27:12</t>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,37 +869,37 @@
         <v>2.94</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S2" t="n">
         <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
         <v>2.7</v>
@@ -917,16 +917,16 @@
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
@@ -965,22 +965,22 @@
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
         <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
@@ -989,31 +989,31 @@
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1022,7 +1022,7 @@
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
@@ -1034,22 +1034,22 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>2.52</v>
       </c>
       <c r="BN2" t="n">
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
         <v>8</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
         <v>9.4</v>
@@ -1058,29 +1058,29 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
         <v>8.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
         <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1135,16 +1135,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.1</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,229 +1864,229 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2118,229 +2118,229 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.86</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH8" t="n">
         <v>4.6</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,261 +2604,515 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:44:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Hafnarfjordur</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Stjarnan</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-07-01 11:35:30</t>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
         <v>2.52</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I2" t="n">
         <v>2.94</v>
@@ -875,7 +875,7 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -890,7 +890,7 @@
         <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.66</v>
@@ -902,13 +902,13 @@
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
         <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
@@ -917,43 +917,43 @@
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="n">
         <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
         <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
         <v>60</v>
@@ -962,55 +962,55 @@
         <v>14.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>9.6</v>
@@ -1022,7 +1022,7 @@
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
@@ -1034,16 +1034,16 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.52</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
         <v>8</v>
@@ -1058,29 +1058,29 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW2" t="n">
         <v>8.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
         <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="I4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,64 +1389,64 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
@@ -1458,137 +1458,137 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="n">
         <v>70</v>
       </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>65</v>
-      </c>
       <c r="AO4" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.5</v>
+        <v>3.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.21</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
@@ -1670,7 +1670,7 @@
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -2151,124 +2151,124 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R7" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="U7" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AM7" t="n">
         <v>55</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP7" t="n">
         <v>28</v>
       </c>
-      <c r="AP7" t="n">
-        <v>27</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS7" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -2277,70 +2277,70 @@
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK7" t="n">
         <v>4.5</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BN7" t="n">
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H8" t="n">
         <v>2.44</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.6</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.88</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
@@ -2423,121 +2423,121 @@
         <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.53</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.59</v>
-      </c>
       <c r="X8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>15</v>
       </c>
-      <c r="AE8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AJ8" t="n">
         <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN8" t="n">
         <v>15.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF8" t="n">
         <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>10</v>
       </c>
       <c r="BG8" t="n">
         <v>11.5</v>
@@ -2546,7 +2546,7 @@
         <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.4</v>
@@ -2558,43 +2558,43 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY8" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2650,19 +2650,19 @@
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
         <v>3.25</v>
@@ -2671,184 +2671,184 @@
         <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,261 +2858,2801 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Wexford F.C</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>St Patricks</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Galway Utd</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Hafnarfjordur</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Stjarnan</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-07-01 13:44:07</t>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -860,7 +860,7 @@
         <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
         <v>2.68</v>
@@ -896,7 +896,7 @@
         <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.52</v>
@@ -908,7 +908,7 @@
         <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
@@ -980,10 +980,10 @@
         <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>7.4</v>
@@ -995,7 +995,7 @@
         <v>5.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
         <v>7.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q3" t="n">
         <v>1.38</v>
@@ -1162,7 +1162,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,34 +1389,34 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>2.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1431,7 +1431,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1443,10 +1443,10 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
@@ -1458,137 +1458,137 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM4" t="n">
         <v>85</v>
       </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
       <c r="AN4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO4" t="n">
         <v>970</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BA4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BB4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1670,7 +1670,7 @@
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S7" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="T7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="V7" t="n">
         <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
         <v>42</v>
@@ -2187,7 +2187,7 @@
         <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
         <v>150</v>
@@ -2199,7 +2199,7 @@
         <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
         <v>48</v>
@@ -2208,7 +2208,7 @@
         <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
         <v>970</v>
@@ -2220,73 +2220,73 @@
         <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
         <v>23</v>
       </c>
       <c r="AM7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN7" t="n">
         <v>5.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
         <v>6.2</v>
@@ -2310,7 +2310,7 @@
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>11</v>
@@ -2322,7 +2322,7 @@
         <v>17</v>
       </c>
       <c r="BS7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BT7" t="n">
         <v>9.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
@@ -2429,10 +2429,10 @@
         <v>2.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2552,28 +2552,28 @@
         <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>8</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
         <v>9</v>
@@ -2582,19 +2582,19 @@
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>24</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.18</v>
@@ -2665,40 +2665,40 @@
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U9" t="n">
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
         <v>44</v>
       </c>
       <c r="Y9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" t="n">
         <v>27</v>
       </c>
-      <c r="Z9" t="n">
-        <v>29</v>
-      </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB9" t="n">
         <v>30</v>
@@ -2707,10 +2707,10 @@
         <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
         <v>34</v>
@@ -2722,7 +2722,7 @@
         <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ9" t="n">
         <v>55</v>
@@ -2740,7 +2740,7 @@
         <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2770,7 +2770,7 @@
         <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>9.800000000000001</v>
@@ -2791,7 +2791,7 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
         <v>7</v>
@@ -2800,40 +2800,40 @@
         <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU9" t="n">
         <v>5.6</v>
@@ -2842,7 +2842,7 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2901,13 +2901,13 @@
         <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2919,7 +2919,7 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.72</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -3152,25 +3152,25 @@
         <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
         <v>2.28</v>
@@ -3179,184 +3179,184 @@
         <v>1.68</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3436,7 +3436,7 @@
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T12" t="n">
         <v>1.87</v>
@@ -3568,7 +3568,7 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,13 +3580,13 @@
         <v>4.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BR12" t="n">
         <v>23</v>
@@ -3598,7 +3598,7 @@
         <v>11</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV12" t="n">
         <v>60</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I13" t="n">
         <v>1.63</v>
@@ -3669,16 +3669,16 @@
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
         <v>2.08</v>
@@ -3687,184 +3687,184 @@
         <v>1.82</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>4.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="n">
         <v>1.73</v>
@@ -3923,202 +3923,202 @@
         <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -4159,220 +4159,220 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -4413,220 +4413,220 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -4667,220 +4667,220 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -4939,16 +4939,16 @@
         <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
         <v>2.34</v>
@@ -4957,184 +4957,184 @@
         <v>1.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -5175,220 +5175,220 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -5447,202 +5447,202 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
@@ -1141,7 +1141,7 @@
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
         <v>1.38</v>
@@ -1162,7 +1162,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.21</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1670,7 +1670,7 @@
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>1.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1924,7 +1924,7 @@
         <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
         <v>1.79</v>
@@ -2157,13 +2157,13 @@
         <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q7" t="n">
         <v>1.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
         <v>1.91</v>
@@ -2175,7 +2175,7 @@
         <v>2.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
         <v>2.26</v>
@@ -2310,7 +2310,7 @@
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>17</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
         <v>3.2</v>
@@ -2644,7 +2644,7 @@
         <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2668,13 +2668,13 @@
         <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
         <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.39</v>
@@ -2683,7 +2683,7 @@
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="AA9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
         <v>30</v>
@@ -2743,43 +2743,43 @@
         <v>9.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>18.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
         <v>19.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>18</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
         <v>19</v>
@@ -2788,10 +2788,10 @@
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
         <v>7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
         <v>1.72</v>
@@ -2931,7 +2931,7 @@
         <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
         <v>2.22</v>
@@ -3072,7 +3072,7 @@
         <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>11.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3134,229 +3134,229 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="Z11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
         <v>30</v>
       </c>
-      <c r="AA11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AI11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
         <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3388,37 +3388,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="G12" t="n">
-        <v>1.54</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>4.7</v>
@@ -3430,197 +3430,197 @@
         <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK12" t="n">
         <v>25</v>
       </c>
-      <c r="Y12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AL12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY12" t="n">
         <v>9.6</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AZ12" t="n">
         <v>12</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="BA12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
         <v>26</v>
       </c>
-      <c r="AI12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BV12" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.2</v>
+        <v>1.48</v>
       </c>
       <c r="G13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H13" t="n">
         <v>7</v>
       </c>
-      <c r="H13" t="n">
-        <v>1.59</v>
-      </c>
       <c r="I13" t="n">
-        <v>1.63</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH13" t="n">
         <v>4.1</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>14.5</v>
       </c>
-      <c r="BN13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3896,34 +3896,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="I14" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3935,55 +3935,55 @@
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB14" t="n">
         <v>22</v>
       </c>
-      <c r="AB14" t="n">
-        <v>23</v>
-      </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG14" t="n">
         <v>24</v>
@@ -3995,130 +3995,130 @@
         <v>36</v>
       </c>
       <c r="AJ14" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM14" t="n">
         <v>140</v>
       </c>
-      <c r="AK14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>120</v>
-      </c>
       <c r="AN14" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AO14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC14" t="n">
         <v>12</v>
       </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BP14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BX14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="I15" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.23</v>
@@ -4195,10 +4195,10 @@
         <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="T15" t="n">
         <v>1.56</v>
@@ -4207,118 +4207,118 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="n">
         <v>5</v>
@@ -4330,13 +4330,13 @@
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BN15" t="n">
         <v>11</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BT15" t="n">
         <v>6</v>
@@ -4366,13 +4366,13 @@
         <v>16.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX15" t="n">
         <v>34</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -4404,229 +4404,229 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7</v>
+        <v>2.88</v>
       </c>
       <c r="H16" t="n">
-        <v>1.72</v>
+        <v>2.78</v>
       </c>
       <c r="I16" t="n">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="J16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.75</v>
       </c>
-      <c r="K16" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.96</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
         <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="BJ16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>1.37</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.4</v>
+        <v>1.37</v>
       </c>
       <c r="BN16" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.7</v>
+        <v>1.37</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>1.37</v>
       </c>
       <c r="BT16" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.5</v>
+        <v>1.37</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.6</v>
+        <v>1.37</v>
       </c>
       <c r="BX16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.4</v>
+        <v>1.37</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>1.88</v>
       </c>
       <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX17" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,184 +4912,184 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
         <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="X18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
         <v>1.01</v>
@@ -5101,13 +5101,13 @@
         <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
         <v>1.01</v>
@@ -5119,7 +5119,7 @@
         <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
         <v>1.01</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,229 +5166,229 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>5.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="W19" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,261 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Loudoun United FC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
@@ -926,7 +926,7 @@
         <v>20</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
@@ -938,10 +938,10 @@
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>34</v>
@@ -962,58 +962,58 @@
         <v>14.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1040,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
         <v>23</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.38</v>
@@ -1159,7 +1159,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="I4" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1407,16 +1407,16 @@
         <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1446,10 +1446,10 @@
         <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>32</v>
@@ -1458,137 +1458,137 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
         <v>80</v>
       </c>
-      <c r="AL4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
       <c r="AN4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>4</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BA4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
         <v>3.3</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.21</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1670,7 +1670,7 @@
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
         <v>1.79</v>
@@ -2151,28 +2151,28 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R7" t="n">
         <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="T7" t="n">
         <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
@@ -2274,7 +2274,7 @@
         <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>6.2</v>
@@ -2310,7 +2310,7 @@
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>17</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
         <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="T9" t="n">
         <v>1.39</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -3344,7 +3344,7 @@
         <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -4070,25 +4070,25 @@
         <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4100,25 +4100,25 @@
         <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BV14" t="n">
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX14" t="n">
         <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -4150,76 +4150,76 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="I15" t="n">
         <v>1.88</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.75</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.56</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
         <v>2.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
         <v>24</v>
@@ -4228,52 +4228,52 @@
         <v>23</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
         <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH15" t="n">
         <v>23</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
       </c>
       <c r="AI15" t="n">
         <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AP15" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS15" t="n">
         <v>14</v>
@@ -4282,97 +4282,97 @@
         <v>13.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>7.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>13</v>
-      </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BH15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>11</v>
-      </c>
       <c r="BO15" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.76</v>
+        <v>5.6</v>
       </c>
       <c r="BX15" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.6</v>
+        <v>1.65</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.88</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>2.12</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>2.14</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.87</v>
+        <v>5.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>1.84</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>1.88</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO18" t="n">
         <v>5.5</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U19" t="n">
         <v>2.06</v>
@@ -5277,7 +5277,7 @@
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO19" t="n">
         <v>12</v>
@@ -5289,10 +5289,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AT19" t="n">
         <v>14.5</v>
@@ -5325,7 +5325,7 @@
         <v>5.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
         <v>6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -5652,261 +5652,1277 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Njardvik</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Throttur</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Grotta</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HK Kopavogur</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K22" t="n">
+        <v>950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Aegir</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>950</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Loudoun United FC</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Sporting Club Jacksonville</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F25" t="n">
         <v>1.62</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G25" t="n">
         <v>1.77</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H25" t="n">
         <v>4.8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I25" t="n">
         <v>6.6</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J25" t="n">
         <v>4.2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="O25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.56</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-07-01 20:12:01</t>
+      <c r="R25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -860,7 +860,7 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
         <v>2.74</v>
@@ -878,7 +878,7 @@
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.7</v>
@@ -917,7 +917,7 @@
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
         <v>60</v>
@@ -929,13 +929,13 @@
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -944,16 +944,16 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ2" t="n">
         <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
         <v>60</v>
@@ -962,10 +962,10 @@
         <v>14.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>6.8</v>
@@ -974,10 +974,10 @@
         <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -1001,7 +1001,7 @@
         <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>7.2</v>
@@ -1040,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
         <v>23</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1138,19 +1138,19 @@
         <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
@@ -1652,7 +1652,7 @@
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
         <v>1.79</v>
@@ -2136,7 +2136,7 @@
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>4.3</v>
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
@@ -2157,13 +2157,13 @@
         <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q7" t="n">
         <v>1.39</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S7" t="n">
         <v>1.88</v>
@@ -2172,7 +2172,7 @@
         <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
@@ -2205,7 +2205,7 @@
         <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2217,7 +2217,7 @@
         <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
         <v>970</v>
@@ -2235,16 +2235,16 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR7" t="n">
         <v>7</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AS7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
         <v>14.5</v>
@@ -2256,7 +2256,7 @@
         <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -2268,43 +2268,43 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
         <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>6.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
         <v>5.6</v>
@@ -2316,31 +2316,31 @@
         <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
         <v>17</v>
       </c>
       <c r="BS7" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BT7" t="n">
         <v>9.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.72</v>
@@ -3039,7 +3039,7 @@
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
         <v>9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -3251,16 +3251,16 @@
         <v>180</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
         <v>8.4</v>
@@ -3269,10 +3269,10 @@
         <v>10.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
@@ -3281,10 +3281,10 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -3293,16 +3293,16 @@
         <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
         <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH11" t="n">
         <v>4.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.28</v>
@@ -3424,7 +3424,7 @@
         <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
         <v>2.28</v>
@@ -3562,19 +3562,19 @@
         <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12" t="n">
         <v>5.6</v>
@@ -3586,13 +3586,13 @@
         <v>16</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR12" t="n">
         <v>26</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
         <v>7</v>
@@ -3604,13 +3604,13 @@
         <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3747,7 +3747,7 @@
         <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
         <v>130</v>
@@ -3765,10 +3765,10 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
         <v>8.4</v>
@@ -3780,7 +3780,7 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3792,7 +3792,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>10.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>5.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I15" t="n">
         <v>1.88</v>
@@ -4174,7 +4174,7 @@
         <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -4186,7 +4186,7 @@
         <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
         <v>2.02</v>
@@ -4210,7 +4210,7 @@
         <v>2.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -4231,22 +4231,22 @@
         <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH15" t="n">
         <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ15" t="n">
         <v>140</v>
@@ -4291,7 +4291,7 @@
         <v>13.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -4300,22 +4300,22 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
         <v>7.8</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>2.88</v>
       </c>
       <c r="H16" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
         <v>3.35</v>
@@ -4428,7 +4428,7 @@
         <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
         <v>1.87</v>
@@ -4682,7 +4682,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="I18" t="n">
         <v>1.88</v>
@@ -4936,19 +4936,19 @@
         <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
         <v>2.12</v>
@@ -4963,16 +4963,16 @@
         <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
         <v>2.12</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -5035,46 +5035,46 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>14</v>
+        <v>3.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AY18" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
         <v>40</v>
@@ -5083,58 +5083,58 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -5196,28 +5196,28 @@
         <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
         <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
         <v>2.06</v>
@@ -5232,19 +5232,19 @@
         <v>18</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
         <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AB19" t="n">
         <v>23</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5262,7 +5262,7 @@
         <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ19" t="n">
         <v>140</v>
@@ -5277,7 +5277,7 @@
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="n">
         <v>12</v>
@@ -5316,22 +5316,22 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
         <v>8.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5707,22 +5707,22 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>1.15</v>
+        <v>2.16</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5731,10 +5731,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -5937,58 +5937,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.07</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>2.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.87</v>
       </c>
       <c r="S22" t="n">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.07</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.09</v>
       </c>
       <c r="P23" t="n">
-        <v>1.07</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
         <v>1.09</v>
       </c>
       <c r="R23" t="n">
-        <v>1.07</v>
+        <v>1.81</v>
       </c>
       <c r="S23" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>1.47</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="O24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="S24" t="n">
-        <v>1.12</v>
+        <v>1.77</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6493,7 +6493,7 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="W24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -860,10 +860,10 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
         <v>2.88</v>
@@ -878,40 +878,40 @@
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
         <v>21</v>
@@ -923,10 +923,10 @@
         <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -953,31 +953,31 @@
         <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,37 +998,37 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE2" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,25 +1040,25 @@
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
         <v>23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV2" t="n">
         <v>26</v>
@@ -1070,17 +1070,17 @@
         <v>34</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
         <v>7.2</v>
@@ -1377,10 +1377,10 @@
         <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
         <v>2.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
         <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
         <v>1.58</v>
@@ -1413,7 +1413,7 @@
         <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
@@ -1470,61 +1470,61 @@
         <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>2.14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.9</v>
+        <v>2.02</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.65</v>
+        <v>1.93</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.85</v>
+        <v>2.02</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1536,7 +1536,7 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,19 +1548,19 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
         <v>1.79</v>
@@ -2139,7 +2139,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -2160,19 +2160,19 @@
         <v>2.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
         <v>2.02</v>
       </c>
       <c r="S7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="T7" t="n">
         <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
@@ -2205,7 +2205,7 @@
         <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2217,7 +2217,7 @@
         <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
         <v>970</v>
@@ -2235,7 +2235,7 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.6</v>
@@ -2244,103 +2244,103 @@
         <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="AW7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA7" t="n">
         <v>7</v>
       </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
         <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
         <v>2.58</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
         <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -2447,7 +2447,7 @@
         <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -2459,7 +2459,7 @@
         <v>25</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
         <v>13.5</v>
@@ -2471,10 +2471,10 @@
         <v>29</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2483,82 +2483,82 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO8" t="n">
         <v>13.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2570,10 +2570,10 @@
         <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
         <v>9</v>
@@ -2585,16 +2585,16 @@
         <v>4.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
         <v>2.22</v>
@@ -2668,7 +2668,7 @@
         <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R9" t="n">
         <v>1.96</v>
@@ -2692,13 +2692,13 @@
         <v>44</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
         <v>30</v>
@@ -2743,16 +2743,16 @@
         <v>9.4</v>
       </c>
       <c r="AP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS9" t="n">
         <v>5.7</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
         <v>19.5</v>
@@ -2764,10 +2764,10 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2776,10 +2776,10 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
         <v>19</v>
@@ -2788,7 +2788,7 @@
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
         <v>7</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.199999999999999</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>3.75</v>
       </c>
       <c r="BN9" t="n">
         <v>7.2</v>
@@ -2824,19 +2824,19 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
         <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>5.4</v>
@@ -2907,46 +2907,46 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.24</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.22</v>
       </c>
       <c r="V10" t="n">
         <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
         <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
         <v>42</v>
@@ -2961,10 +2961,10 @@
         <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2979,10 +2979,10 @@
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
@@ -2991,7 +2991,7 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
@@ -3003,10 +3003,10 @@
         <v>18.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
@@ -3018,7 +3018,7 @@
         <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,89 +3030,89 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10" t="n">
         <v>3.95</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.42</v>
       </c>
       <c r="G11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="H11" t="n">
         <v>8.199999999999999</v>
@@ -3155,7 +3155,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K11" t="n">
         <v>5.5</v>
@@ -3167,16 +3167,16 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
         <v>1.53</v>
@@ -3194,19 +3194,19 @@
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="X11" t="n">
         <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z11" t="n">
         <v>95</v>
       </c>
       <c r="AA11" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
@@ -3215,7 +3215,7 @@
         <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE11" t="n">
         <v>150</v>
@@ -3227,10 +3227,10 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
         <v>15</v>
@@ -3248,19 +3248,19 @@
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
         <v>8.4</v>
@@ -3272,7 +3272,7 @@
         <v>4.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
@@ -3281,10 +3281,10 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -3293,43 +3293,43 @@
         <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF11" t="n">
         <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.4</v>
@@ -3338,25 +3338,25 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT11" t="n">
         <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.28</v>
@@ -3406,13 +3406,13 @@
         <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.28</v>
@@ -3427,7 +3427,7 @@
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
         <v>1.68</v>
@@ -3445,7 +3445,7 @@
         <v>2.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
         <v>1.78</v>
@@ -3466,7 +3466,7 @@
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>17</v>
@@ -3475,7 +3475,7 @@
         <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
         <v>13</v>
@@ -3487,7 +3487,7 @@
         <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
         <v>25</v>
@@ -3499,7 +3499,7 @@
         <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
         <v>30</v>
@@ -3514,7 +3514,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
         <v>9.800000000000001</v>
@@ -3526,7 +3526,7 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
@@ -3538,7 +3538,7 @@
         <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
@@ -3547,10 +3547,10 @@
         <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
@@ -3574,19 +3574,19 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN12" t="n">
         <v>5.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>26</v>
@@ -3595,7 +3595,7 @@
         <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU12" t="n">
         <v>5.8</v>
@@ -3604,10 +3604,10 @@
         <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
         <v>7.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3681,7 +3681,7 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
         <v>1.68</v>
@@ -3693,16 +3693,16 @@
         <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="X13" t="n">
         <v>25</v>
@@ -3711,7 +3711,7 @@
         <v>32</v>
       </c>
       <c r="Z13" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="n">
         <v>240</v>
@@ -3729,7 +3729,7 @@
         <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
@@ -3741,10 +3741,10 @@
         <v>100</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL13" t="n">
         <v>34</v>
@@ -3753,10 +3753,10 @@
         <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP13" t="n">
         <v>18.5</v>
@@ -3765,13 +3765,13 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
         <v>9</v>
@@ -3792,52 +3792,52 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
         <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
         <v>5.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ13" t="n">
         <v>5.6</v>
@@ -3846,25 +3846,25 @@
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ13" t="n">
         <v>14.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>7</v>
@@ -3935,13 +3935,13 @@
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
         <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
@@ -3995,7 +3995,7 @@
         <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK14" t="n">
         <v>110</v>
@@ -4010,7 +4010,7 @@
         <v>130</v>
       </c>
       <c r="AO14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP14" t="n">
         <v>15</v>
@@ -4037,7 +4037,7 @@
         <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -4046,22 +4046,22 @@
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BE14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
         <v>6.6</v>
@@ -4070,7 +4070,7 @@
         <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4082,25 +4082,25 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR14" t="n">
         <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT14" t="n">
         <v>3.8</v>
@@ -4118,7 +4118,7 @@
         <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4159,100 +4159,100 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G15" t="n">
         <v>5.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
         <v>1.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
         <v>23</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
         <v>44</v>
       </c>
-      <c r="AG15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>38</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL15" t="n">
         <v>80</v>
@@ -4261,76 +4261,76 @@
         <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="AW15" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC15" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4339,7 +4339,7 @@
         <v>9.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO15" t="n">
         <v>4.7</v>
@@ -4357,19 +4357,19 @@
         <v>8.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV15" t="n">
         <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY15" t="n">
         <v>7.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4413,160 +4413,160 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
         <v>2.88</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="I16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
         <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
         <v>1.53</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV16" t="n">
         <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
         <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4575,58 +4575,58 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.37</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.37</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
         <v>1.87</v>
@@ -4676,211 +4676,211 @@
         <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G18" t="n">
         <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
@@ -4939,7 +4939,7 @@
         <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4969,7 +4969,7 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W18" t="n">
         <v>1.23</v>
@@ -4999,7 +4999,7 @@
         <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AG18" t="n">
         <v>23</v>
@@ -5011,7 +5011,7 @@
         <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="n">
         <v>70</v>
@@ -5029,112 +5029,112 @@
         <v>12.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV18" t="n">
         <v>3.4</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AW18" t="n">
         <v>3.8</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AX18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>3.8</v>
       </c>
-      <c r="AU18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE18" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE18" t="n">
+      <c r="BF18" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>40</v>
       </c>
       <c r="BG18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>4.9</v>
       </c>
       <c r="G19" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H19" t="n">
         <v>1.73</v>
@@ -5193,7 +5193,7 @@
         <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -5205,7 +5205,7 @@
         <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
         <v>1.79</v>
@@ -5214,10 +5214,10 @@
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
         <v>2.06</v>
@@ -5226,7 +5226,7 @@
         <v>2.16</v>
       </c>
       <c r="W19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
         <v>18</v>
@@ -5235,16 +5235,16 @@
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5253,10 +5253,10 @@
         <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AG19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>20</v>
@@ -5268,16 +5268,16 @@
         <v>140</v>
       </c>
       <c r="AK19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="n">
         <v>75</v>
       </c>
       <c r="AM19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="n">
         <v>12</v>
@@ -5289,10 +5289,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT19" t="n">
         <v>14.5</v>
@@ -5304,37 +5304,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
         <v>32</v>
       </c>
       <c r="AY19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19" t="n">
         <v>3.85</v>
@@ -5352,34 +5352,34 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO19" t="n">
         <v>6.8</v>
       </c>
       <c r="BP19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU19" t="n">
         <v>3.9</v>
       </c>
       <c r="BV19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
         <v>9.199999999999999</v>
@@ -5388,7 +5388,7 @@
         <v>26</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5683,230 +5683,230 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X21" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN21" t="n">
         <v>6.4</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>3.5</v>
@@ -5949,218 +5949,218 @@
         <v>2.26</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="P22" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="R22" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="S22" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U22" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W22" t="n">
         <v>1.4</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -6197,46 +6197,46 @@
         <v>4.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="I23" t="n">
         <v>2.06</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
         <v>6.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="O23" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="V23" t="n">
         <v>1.94</v>
@@ -6245,118 +6245,118 @@
         <v>1.29</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ23" t="n">
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
@@ -6380,7 +6380,7 @@
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6392,7 +6392,7 @@
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -6448,227 +6448,227 @@
         <v>7.2</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="I24" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X24" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO24" t="n">
         <v>4.5</v>
       </c>
-      <c r="K24" t="n">
-        <v>110</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="AP24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
         <v>1.76</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -6705,10 +6705,10 @@
         <v>1.77</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J25" t="n">
         <v>4.2</v>
@@ -6717,94 +6717,94 @@
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP25" t="n">
         <v>1.03</v>
@@ -6855,74 +6855,74 @@
         <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG25" t="n">
         <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
         <v>2.6</v>
@@ -881,19 +881,19 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
         <v>2.42</v>
@@ -902,7 +902,7 @@
         <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
@@ -920,13 +920,13 @@
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -950,7 +950,7 @@
         <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
         <v>38</v>
@@ -962,31 +962,31 @@
         <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR2" t="n">
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX2" t="n">
         <v>6.8</v>
@@ -998,37 +998,37 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
         <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
         <v>23</v>
@@ -1064,7 +1064,7 @@
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>34</v>
@@ -1073,14 +1073,14 @@
         <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
         <v>5.6</v>
@@ -1413,7 +1413,7 @@
         <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
@@ -1473,58 +1473,58 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AR4" t="n">
         <v>2.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.76</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1742,7 +1742,7 @@
         <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
         <v>1.03</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.16</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
         <v>42</v>
@@ -2205,7 +2205,7 @@
         <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2217,7 +2217,7 @@
         <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
         <v>970</v>
@@ -2250,7 +2250,7 @@
         <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>18.5</v>
@@ -2259,7 +2259,7 @@
         <v>7.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
@@ -2289,58 +2289,58 @@
         <v>16.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
         <v>2.58</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
         <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="V8" t="n">
         <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
         <v>27</v>
@@ -2483,82 +2483,82 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
         <v>13.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AT8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2576,7 +2576,7 @@
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
@@ -2668,13 +2668,13 @@
         <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
         <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="T9" t="n">
         <v>1.39</v>
@@ -2683,118 +2683,118 @@
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z9" t="n">
         <v>24</v>
       </c>
-      <c r="Z9" t="n">
-        <v>26</v>
-      </c>
       <c r="AA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF9" t="n">
         <v>32</v>
       </c>
-      <c r="AB9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>34</v>
-      </c>
       <c r="AG9" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
         <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
         <v>9.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.7</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
         <v>19.5</v>
       </c>
-      <c r="AU9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="BB9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>10</v>
-      </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="n">
         <v>5.6</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="BN9" t="n">
         <v>7.2</v>
@@ -2824,13 +2824,13 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
         <v>6.4</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
         <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2919,16 +2919,16 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
         <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
@@ -2973,7 +2973,7 @@
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>60</v>
@@ -2988,7 +2988,7 @@
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
         <v>8.4</v>
@@ -3003,13 +3003,13 @@
         <v>18.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT10" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
         <v>8.6</v>
@@ -3018,7 +3018,7 @@
         <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3042,13 +3042,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
         <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH10" t="n">
         <v>3.95</v>
@@ -3057,7 +3057,7 @@
         <v>3.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK10" t="n">
         <v>6.4</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
@@ -3078,13 +3078,13 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -3170,16 +3170,16 @@
         <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
         <v>2.64</v>
@@ -3194,25 +3194,25 @@
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
         <v>36</v>
       </c>
       <c r="Z11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA11" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>38</v>
@@ -3251,28 +3251,28 @@
         <v>170</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR11" t="n">
         <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
         <v>8.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
@@ -3281,34 +3281,34 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
         <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
@@ -3323,10 +3323,10 @@
         <v>13</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP11" t="n">
         <v>8.6</v>
@@ -3344,7 +3344,7 @@
         <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
         <v>2.28</v>
@@ -3406,7 +3406,7 @@
         <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
@@ -3439,13 +3439,13 @@
         <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
         <v>2.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
         <v>1.78</v>
@@ -3460,7 +3460,7 @@
         <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
         <v>14.5</v>
@@ -3508,43 +3508,43 @@
         <v>17.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
         <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
         <v>7.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
         <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
         <v>5</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>4.9</v>
@@ -3553,10 +3553,10 @@
         <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
         <v>5.6</v>
@@ -3586,16 +3586,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR12" t="n">
         <v>26</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU12" t="n">
         <v>5.8</v>
@@ -3604,13 +3604,13 @@
         <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G13" t="n">
         <v>1.51</v>
@@ -3666,7 +3666,7 @@
         <v>4.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
@@ -3675,7 +3675,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.24</v>
@@ -3684,19 +3684,19 @@
         <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
@@ -3753,7 +3753,7 @@
         <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO13" t="n">
         <v>150</v>
@@ -3762,13 +3762,13 @@
         <v>18.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="AR13" t="n">
         <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3777,40 +3777,40 @@
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE13" t="n">
         <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4</v>
@@ -3822,13 +3822,13 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN13" t="n">
         <v>4.1</v>
@@ -3840,16 +3840,16 @@
         <v>9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU13" t="n">
         <v>6.4</v>
@@ -3858,23 +3858,23 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
         <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
         <v>1.59</v>
@@ -3950,13 +3950,13 @@
         <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V14" t="n">
         <v>2.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -4010,13 +4010,13 @@
         <v>130</v>
       </c>
       <c r="AO14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
         <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
         <v>8.800000000000001</v>
@@ -4025,7 +4025,7 @@
         <v>13.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU14" t="n">
         <v>8.6</v>
@@ -4037,7 +4037,7 @@
         <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -4046,22 +4046,22 @@
         <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
         <v>6.6</v>
@@ -4070,7 +4070,7 @@
         <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
@@ -4082,25 +4082,25 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR14" t="n">
         <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT14" t="n">
         <v>3.8</v>
@@ -4118,7 +4118,7 @@
         <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4162,169 +4162,169 @@
         <v>4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
         <v>1.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
         <v>2.92</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="V15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
         <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
@@ -4336,43 +4336,43 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT15" t="n">
         <v>4.7</v>
       </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BU15" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BV15" t="n">
         <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BX15" t="n">
         <v>27</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4431,13 +4431,13 @@
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
@@ -4446,7 +4446,7 @@
         <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
         <v>1.27</v>
@@ -4455,7 +4455,7 @@
         <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
         <v>1.98</v>
@@ -4482,16 +4482,16 @@
         <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -4506,7 +4506,7 @@
         <v>50</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
@@ -4527,10 +4527,10 @@
         <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
         <v>7.2</v>
@@ -4539,46 +4539,46 @@
         <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BH16" t="n">
         <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4590,13 +4590,13 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.71</v>
+        <v>2.42</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4608,25 +4608,25 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.65</v>
+        <v>8.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.66</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4667,220 +4667,220 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H17" t="n">
         <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
         <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.7</v>
+        <v>1.22</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4921,220 +4921,220 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="G18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="I18" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G19" t="n">
         <v>5.5</v>
@@ -5205,7 +5205,7 @@
         <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
         <v>1.79</v>
@@ -5220,7 +5220,7 @@
         <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>2.16</v>
@@ -5238,13 +5238,13 @@
         <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB19" t="n">
         <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
@@ -5268,7 +5268,7 @@
         <v>140</v>
       </c>
       <c r="AK19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL19" t="n">
         <v>75</v>
@@ -5289,10 +5289,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT19" t="n">
         <v>14.5</v>
@@ -5307,7 +5307,7 @@
         <v>14</v>
       </c>
       <c r="AX19" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -5316,22 +5316,22 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG19" t="n">
         <v>8.800000000000001</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>2.54</v>
       </c>
       <c r="I21" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
@@ -5713,22 +5713,22 @@
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
         <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
         <v>1.47</v>
       </c>
       <c r="U21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V21" t="n">
         <v>1.51</v>
@@ -5737,7 +5737,7 @@
         <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y21" t="n">
         <v>22</v>
@@ -5755,10 +5755,10 @@
         <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
@@ -5767,10 +5767,10 @@
         <v>15.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AJ21" t="n">
         <v>44</v>
@@ -5785,67 +5785,67 @@
         <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4</v>
       </c>
-      <c r="AR21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT21" t="n">
+      <c r="BD21" t="n">
         <v>4</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BE21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF21" t="n">
         <v>3.55</v>
       </c>
-      <c r="AV21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BG21" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI21" t="n">
         <v>3.3</v>
@@ -5854,31 +5854,31 @@
         <v>8.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
         <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR21" t="n">
         <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT21" t="n">
         <v>6.6</v>
@@ -5890,23 +5890,23 @@
         <v>18.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX21" t="n">
         <v>25</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ21" t="n">
         <v>15</v>
       </c>
       <c r="CA21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -5940,46 +5940,46 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I22" t="n">
         <v>2.26</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
         <v>4.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
         <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="T22" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="U22" t="n">
         <v>2.9</v>
@@ -5988,25 +5988,25 @@
         <v>1.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="n">
         <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD22" t="n">
         <v>14</v>
@@ -6030,7 +6030,7 @@
         <v>65</v>
       </c>
       <c r="AK22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
         <v>36</v>
@@ -6045,97 +6045,97 @@
         <v>9</v>
       </c>
       <c r="AP22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS22" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AT22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY22" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AZ22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF22" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="BG22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI22" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.5</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN22" t="n">
         <v>7.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP22" t="n">
         <v>22</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU22" t="n">
         <v>3.75</v>
@@ -6144,23 +6144,23 @@
         <v>14</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -6194,19 +6194,19 @@
         <v>3.35</v>
       </c>
       <c r="G23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="I23" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.2</v>
@@ -6224,7 +6224,7 @@
         <v>2.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
         <v>1.83</v>
@@ -6233,13 +6233,13 @@
         <v>1.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
         <v>2.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W23" t="n">
         <v>1.29</v>
@@ -6248,7 +6248,7 @@
         <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
         <v>21</v>
@@ -6278,28 +6278,28 @@
         <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL23" t="n">
         <v>40</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>38</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
         <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>4.1</v>
@@ -6317,7 +6317,7 @@
         <v>3.75</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
@@ -6332,10 +6332,10 @@
         <v>3.95</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC23" t="n">
         <v>4.5</v>
@@ -6344,10 +6344,10 @@
         <v>4.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
         <v>3.05</v>
@@ -6356,7 +6356,7 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
@@ -6380,7 +6380,7 @@
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6392,7 +6392,7 @@
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G24" t="n">
         <v>12.5</v>
@@ -6457,7 +6457,7 @@
         <v>1.4</v>
       </c>
       <c r="J24" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="K24" t="n">
         <v>8.4</v>
@@ -6466,49 +6466,49 @@
         <v>1.18</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="R24" t="n">
         <v>1.83</v>
       </c>
       <c r="S24" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V24" t="n">
         <v>3.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y24" t="n">
         <v>970</v>
       </c>
       <c r="Z24" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AB24" t="n">
         <v>55</v>
@@ -6517,7 +6517,7 @@
         <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>970</v>
@@ -6529,10 +6529,10 @@
         <v>42</v>
       </c>
       <c r="AH24" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
@@ -6550,61 +6550,61 @@
         <v>120</v>
       </c>
       <c r="AO24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AP24" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="BH24" t="n">
         <v>5.6</v>
@@ -6613,7 +6613,7 @@
         <v>3.6</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK24" t="n">
         <v>5.3</v>
@@ -6625,7 +6625,7 @@
         <v>1.76</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BO24" t="n">
         <v>5.8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -6702,13 +6702,13 @@
         <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J25" t="n">
         <v>4.2</v>
@@ -6723,34 +6723,34 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="U25" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X25" t="n">
         <v>30</v>
@@ -6786,10 +6786,10 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
         <v>19.5</v>
@@ -6801,16 +6801,16 @@
         <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>1.03</v>
@@ -6819,37 +6819,37 @@
         <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW25" t="n">
         <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
         <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE25" t="n">
         <v>1.03</v>
@@ -6858,7 +6858,7 @@
         <v>5.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH25" t="n">
         <v>4.5</v>
@@ -6867,7 +6867,7 @@
         <v>3.35</v>
       </c>
       <c r="BJ25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK25" t="n">
         <v>6.8</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
         <v>4.8</v>
@@ -6897,7 +6897,7 @@
         <v>15</v>
       </c>
       <c r="BT25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU25" t="n">
         <v>6.6</v>
@@ -6906,7 +6906,7 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>2.6</v>
@@ -911,7 +911,7 @@
         <v>1.62</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
         <v>21</v>
@@ -920,16 +920,16 @@
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB2" t="n">
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>32</v>
@@ -965,16 +965,16 @@
         <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>15</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>14</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,25 +998,25 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC2" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
         <v>1.31</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
         <v>1.31</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="G4" t="n">
         <v>7.2</v>
@@ -1374,13 +1374,13 @@
         <v>1.54</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,19 +1389,19 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="Q4" t="n">
         <v>1.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S4" t="n">
         <v>2.12</v>
@@ -1410,13 +1410,13 @@
         <v>1.58</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1452,7 +1452,7 @@
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.32</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA4" t="n">
         <v>2.44</v>
       </c>
-      <c r="AU4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.42</v>
-      </c>
       <c r="BB4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BC4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF4" t="n">
         <v>2.54</v>
       </c>
-      <c r="BD4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
@@ -1670,7 +1670,7 @@
         <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1882,7 +1882,7 @@
         <v>1.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.16</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="T7" t="n">
         <v>1.45</v>
@@ -2175,10 +2175,10 @@
         <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X7" t="n">
         <v>42</v>
@@ -2196,7 +2196,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD7" t="n">
         <v>27</v>
@@ -2235,28 +2235,28 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS7" t="n">
         <v>7</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
         <v>11.5</v>
@@ -2268,10 +2268,10 @@
         <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -2280,10 +2280,10 @@
         <v>15.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BG7" t="n">
         <v>16.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>2.58</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
@@ -2411,16 +2411,16 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
         <v>1.52</v>
@@ -2432,22 +2432,22 @@
         <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC8" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
         <v>24</v>
@@ -2471,7 +2471,7 @@
         <v>29</v>
       </c>
       <c r="AJ8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
@@ -2483,10 +2483,10 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -2498,13 +2498,13 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
         <v>9.4</v>
@@ -2525,22 +2525,22 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.28</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
@@ -2683,22 +2683,22 @@
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
         <v>27</v>
@@ -2737,10 +2737,10 @@
         <v>40</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AP9" t="n">
         <v>10</v>
@@ -2767,7 +2767,7 @@
         <v>17.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY9" t="n">
         <v>12.5</v>
@@ -2782,10 +2782,10 @@
         <v>40</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2794,13 +2794,13 @@
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.199999999999999</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>7.2</v>
@@ -2824,13 +2824,13 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>6.4</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
         <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2931,7 +2931,7 @@
         <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
         <v>2.24</v>
@@ -3006,7 +3006,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3051,22 +3051,22 @@
         <v>9.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
@@ -3078,13 +3078,13 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>14</v>
       </c>
       <c r="BZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G11" t="n">
         <v>1.45</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.48</v>
       </c>
       <c r="H11" t="n">
         <v>8.199999999999999</v>
@@ -3155,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>5.4</v>
@@ -3170,19 +3170,19 @@
         <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
         <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
         <v>1.9</v>
@@ -3194,7 +3194,7 @@
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X11" t="n">
         <v>26</v>
@@ -3206,7 +3206,7 @@
         <v>90</v>
       </c>
       <c r="AA11" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
@@ -3248,10 +3248,10 @@
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.4</v>
@@ -3263,7 +3263,7 @@
         <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
@@ -3278,19 +3278,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
         <v>4.8</v>
       </c>
       <c r="BB11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC11" t="n">
         <v>11</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>4.5</v>
@@ -3299,7 +3299,7 @@
         <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
         <v>4.9</v>
@@ -3344,7 +3344,7 @@
         <v>12</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
         <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>13</v>
       </c>
-      <c r="AH12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="BD12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF12" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI12" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS12" t="n">
         <v>9.4</v>
       </c>
-      <c r="BN12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BT12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.51</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>7.6</v>
       </c>
-      <c r="I13" t="n">
+      <c r="AR13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU13" t="n">
         <v>8.6</v>
       </c>
-      <c r="J13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AV13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX13" t="n">
         <v>25</v>
       </c>
-      <c r="Y13" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="BY13" t="n">
         <v>10</v>
       </c>
-      <c r="AV13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ13" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3896,229 +3896,229 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="I14" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
         <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AA14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AT14" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY14" t="n">
         <v>15</v>
       </c>
-      <c r="AX14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>21</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY14" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4159,166 +4159,166 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="I15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J15" t="n">
         <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="n">
         <v>3.8</v>
@@ -4360,13 +4360,13 @@
         <v>4.7</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BV15" t="n">
         <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15" t="n">
         <v>27</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4404,229 +4404,229 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="H16" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE16" t="n">
         <v>65</v>
       </c>
-      <c r="AB16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>48</v>
-      </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO16" t="n">
         <v>60</v>
       </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>48</v>
-      </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.68</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.7</v>
+        <v>13.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.84</v>
+        <v>12.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.68</v>
+        <v>4.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BU16" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.26</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
         <v>4.4</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO17" t="n">
         <v>6</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV17" t="n">
         <v>12.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO18" t="n">
         <v>3.75</v>
       </c>
-      <c r="G18" t="n">
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BT18" t="n">
         <v>6.2</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5161,192 +5161,192 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="n">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="H19" t="n">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.79</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
         <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="n">
-        <v>80</v>
+        <v>14.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AP19" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BI19" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,40 +5355,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BX19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5707,16 +5707,16 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.65</v>
@@ -5725,7 +5725,7 @@
         <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U21" t="n">
         <v>2.66</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -5946,19 +5946,19 @@
         <v>2.02</v>
       </c>
       <c r="I22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K22" t="n">
         <v>4.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
         <v>3.45</v>
@@ -5967,7 +5967,7 @@
         <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
         <v>1.41</v>
@@ -5982,13 +5982,13 @@
         <v>1.44</v>
       </c>
       <c r="U22" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X22" t="n">
         <v>40</v>
@@ -6003,7 +6003,7 @@
         <v>32</v>
       </c>
       <c r="AB22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC22" t="n">
         <v>13.5</v>
@@ -6021,10 +6021,10 @@
         <v>18</v>
       </c>
       <c r="AH22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ22" t="n">
         <v>65</v>
@@ -6036,73 +6036,73 @@
         <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AQ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS22" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AT22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX22" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AY22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB22" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5</v>
-      </c>
       <c r="BC22" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BH22" t="n">
         <v>5.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -6191,70 +6191,70 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
         <v>4.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="I23" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R23" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S23" t="n">
         <v>1.94</v>
       </c>
       <c r="T23" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U23" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V23" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X23" t="n">
         <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB23" t="n">
         <v>32</v>
@@ -6266,7 +6266,7 @@
         <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AF23" t="n">
         <v>42</v>
@@ -6278,79 +6278,79 @@
         <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
         <v>80</v>
       </c>
       <c r="AK23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
         <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV23" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AW23" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>12.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I24" t="n">
         <v>1.4</v>
@@ -6460,7 +6460,7 @@
         <v>5.3</v>
       </c>
       <c r="K24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>1.18</v>
@@ -6478,13 +6478,13 @@
         <v>2.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="T24" t="n">
         <v>1.71</v>
@@ -6523,7 +6523,7 @@
         <v>970</v>
       </c>
       <c r="AF24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AG24" t="n">
         <v>42</v>
@@ -6553,7 +6553,7 @@
         <v>4</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>5.2</v>
@@ -6562,49 +6562,49 @@
         <v>4.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV24" t="n">
         <v>4.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="BC24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD24" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="BH24" t="n">
         <v>5.6</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -6702,13 +6702,13 @@
         <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H25" t="n">
         <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
         <v>4.2</v>
@@ -6747,7 +6747,7 @@
         <v>2.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
         <v>2.28</v>
@@ -6807,10 +6807,10 @@
         <v>65</v>
       </c>
       <c r="AP25" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
         <v>1.03</v>
@@ -6819,34 +6819,34 @@
         <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV25" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW25" t="n">
         <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
         <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD25" t="n">
         <v>20</v>
@@ -6855,7 +6855,7 @@
         <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG25" t="n">
         <v>36</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -878,46 +878,46 @@
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z2" t="n">
         <v>25</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>23</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
@@ -926,7 +926,7 @@
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
@@ -956,19 +956,19 @@
         <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AO2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>16</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>15</v>
       </c>
       <c r="AR2" t="n">
         <v>7.6</v>
@@ -977,7 +977,7 @@
         <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU2" t="n">
         <v>8.6</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,10 +998,10 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>7.6</v>
@@ -1010,19 +1010,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
         <v>5.4</v>
@@ -1049,7 +1049,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS2" t="n">
         <v>9.6</v>
@@ -1058,29 +1058,29 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
@@ -1147,7 +1147,7 @@
         <v>1.31</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
         <v>1.31</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
@@ -1404,7 +1404,7 @@
         <v>1.73</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.58</v>
@@ -1419,7 +1419,7 @@
         <v>1.19</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1473,58 +1473,58 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AS4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA4" t="n">
         <v>3.85</v>
       </c>
-      <c r="AT4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BB4" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>1.49</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1873,100 +1873,100 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.3</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.25</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1978,61 +1978,61 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
         <v>1.76</v>
@@ -2166,10 +2166,10 @@
         <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="U7" t="n">
         <v>2.96</v>
@@ -2199,10 +2199,10 @@
         <v>15.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
         <v>17</v>
@@ -2214,40 +2214,40 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR7" t="n">
         <v>28</v>
       </c>
-      <c r="AK7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AS7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT7" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>9.4</v>
@@ -2256,31 +2256,31 @@
         <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
         <v>11.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
         <v>18.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
         <v>3.75</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
@@ -2423,7 +2423,7 @@
         <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
         <v>2.68</v>
@@ -2432,64 +2432,64 @@
         <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE8" t="n">
         <v>26</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AF8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AI8" t="n">
         <v>34</v>
       </c>
-      <c r="AB8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>29</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>12.5</v>
@@ -2498,22 +2498,22 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX8" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>18</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2525,16 +2525,16 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>38</v>
+        <v>5.3</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
@@ -2644,7 +2644,7 @@
         <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>4.4</v>
@@ -2683,7 +2683,7 @@
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
         <v>1.49</v>
@@ -2701,7 +2701,7 @@
         <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2800,7 +2800,7 @@
         <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.199999999999999</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2895,76 +2895,76 @@
         <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
         <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
         <v>2.28</v>
       </c>
       <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="n">
         <v>23</v>
       </c>
-      <c r="Y10" t="n">
-        <v>22</v>
-      </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>650</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2976,7 +2976,7 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>610</v>
       </c>
       <c r="AJ10" t="n">
         <v>18</v>
@@ -2985,31 +2985,31 @@
         <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>530</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>18.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AS10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="n">
         <v>10</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
         <v>8.6</v>
@@ -3018,19 +3018,19 @@
         <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3039,87 +3039,87 @@
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BF10" t="n">
         <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
       </c>
       <c r="BI10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO10" t="n">
         <v>3.65</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BP10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -3388,178 +3388,178 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
         <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA12" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI12" t="n">
         <v>120</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>100</v>
       </c>
       <c r="AJ12" t="n">
         <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI12" t="n">
         <v>3.25</v>
@@ -3568,59 +3568,59 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BP12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
         <v>9</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BT12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>1.46</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.59</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.63</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.99</v>
       </c>
       <c r="V13" t="n">
-        <v>2.58</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK13" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>110</v>
-      </c>
       <c r="AL13" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AM13" t="n">
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>130</v>
+        <v>6.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AV13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>21</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC13" t="n">
         <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -3896,229 +3896,229 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="I14" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
         <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="V14" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO14" t="n">
         <v>11</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AP14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE14" t="n">
+      <c r="AT14" t="n">
         <v>19</v>
       </c>
-      <c r="AF14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AU14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG14" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BN14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,187 +4150,187 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="I15" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG15" t="n">
         <v>21</v>
       </c>
-      <c r="Y15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW15" t="n">
         <v>14</v>
       </c>
-      <c r="AA15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AX15" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,16 +4342,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BQ15" t="n">
         <v>8</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS15" t="n">
         <v>8.199999999999999</v>
@@ -4366,10 +4366,10 @@
         <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY15" t="n">
         <v>7.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -4404,187 +4404,187 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.69</v>
+        <v>4.7</v>
       </c>
       <c r="G16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I16" t="n">
         <v>1.87</v>
       </c>
-      <c r="H16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5.3</v>
-      </c>
       <c r="J16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.95</v>
       </c>
-      <c r="K16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>2.14</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AB16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>14</v>
       </c>
-      <c r="AC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="BD16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4593,40 +4593,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>8</v>
-      </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE17" t="n">
         <v>4.4</v>
       </c>
-      <c r="G17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="BF17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.3</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X17" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH17" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
         <v>9.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP17" t="n">
         <v>12</v>
       </c>
-      <c r="BN17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="G18" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.86</v>
+        <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB18" t="n">
         <v>4</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X18" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS18" t="n">
+      <c r="BC18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT18" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BU18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW18" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,234 +5161,234 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>2.94</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
         <v>60</v>
       </c>
-      <c r="AB19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>36</v>
-      </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>13</v>
-      </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BC19" t="n">
-        <v>17.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>7</v>
-      </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="BP19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BT19" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR19" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>7</v>
-      </c>
       <c r="BU19" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,234 +5415,234 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.07</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="T21" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="H22" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="I22" t="n">
-        <v>2.28</v>
+        <v>2.96</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="S22" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="U22" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="V22" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AA22" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AB22" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AC22" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AF22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI22" t="n">
         <v>36</v>
       </c>
-      <c r="AG22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO22" t="n">
         <v>17</v>
       </c>
-      <c r="AI22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AP22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AQ22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC22" t="n">
         <v>4</v>
       </c>
-      <c r="AR22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS22" t="n">
+      <c r="BD22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE22" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="BF22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG22" t="n">
         <v>3.65</v>
       </c>
-      <c r="AV22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG22" t="n">
+      <c r="BH22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI22" t="n">
         <v>3.3</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.45</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP22" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS22" t="n">
         <v>7.2</v>
       </c>
       <c r="BT22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BV22" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -6182,239 +6182,239 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="I23" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="S23" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="T23" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U23" t="n">
         <v>2.8</v>
       </c>
       <c r="V23" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="W23" t="n">
         <v>1.31</v>
       </c>
       <c r="X23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y23" t="n">
         <v>20</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB23" t="n">
         <v>32</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AF23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK23" t="n">
         <v>42</v>
       </c>
-      <c r="AG23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>40</v>
-      </c>
       <c r="AL23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BC23" t="n">
+      <c r="BD23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW23" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -6436,67 +6436,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="G24" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="J24" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="K24" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="S24" t="n">
         <v>1.89</v>
       </c>
       <c r="T24" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>2.84</v>
       </c>
       <c r="V24" t="n">
-        <v>3.45</v>
+        <v>2.16</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
         <v>46</v>
@@ -6505,424 +6505,932 @@
         <v>970</v>
       </c>
       <c r="Z24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>16</v>
       </c>
-      <c r="AA24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AR24" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV24" t="n">
         <v>5</v>
       </c>
-      <c r="AT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW24" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aegir</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>KFG</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Selfoss</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K26" t="n">
+        <v>950</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>US United Soccer League</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Loudoun United FC</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Sporting Club Jacksonville</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.77</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>4.8</v>
       </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J27" t="n">
         <v>4.2</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>5</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L27" t="n">
         <v>1.24</v>
       </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
         <v>5.1</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>1.19</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.56</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.64</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>2.26</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>1.21</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>2.28</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>30</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y27" t="n">
         <v>29</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z27" t="n">
         <v>55</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AA27" t="n">
         <v>140</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB27" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC27" t="n">
         <v>13</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AD27" t="n">
         <v>25</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AE27" t="n">
         <v>70</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF27" t="n">
         <v>15</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AG27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AH27" t="n">
         <v>22</v>
       </c>
-      <c r="AI25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK25" t="n">
+      <c r="AI27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK27" t="n">
         <v>19.5</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AL27" t="n">
         <v>34</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AM27" t="n">
         <v>90</v>
       </c>
-      <c r="AN25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AN27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD27" t="n">
         <v>20</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="BE27" t="n">
         <v>1.03</v>
       </c>
-      <c r="AS25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX25" t="n">
+      <c r="BF27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>28</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>15</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-07-02 07:01:44</t>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -863,7 +863,7 @@
         <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
         <v>2.86</v>
@@ -881,82 +881,82 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
         <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W2" t="n">
         <v>1.63</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
         <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
         <v>30</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>12.5</v>
@@ -965,16 +965,16 @@
         <v>14.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="AT2" t="n">
         <v>15</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,89 +998,89 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BE2" t="n">
         <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>14.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="T3" t="n">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,34 +1177,34 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1273,16 +1273,16 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,28 +1291,28 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
         <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="I4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1443,16 +1443,16 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1464,37 +1464,37 @@
         <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO4" t="n">
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AT4" t="n">
         <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AX4" t="n">
         <v>4.1</v>
@@ -1503,92 +1503,92 @@
         <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
         <v>4.1</v>
       </c>
       <c r="BE4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF4" t="n">
-        <v>4</v>
-      </c>
       <c r="BG4" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1652,13 +1652,13 @@
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="H6" t="n">
+      <c r="L6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.86</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1936,7 +1936,7 @@
         <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
@@ -1948,25 +1948,25 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AF6" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AG6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1981,58 +1981,58 @@
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AS6" t="n">
         <v>4.3</v>
       </c>
       <c r="AT6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4</v>
       </c>
-      <c r="AU6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.8</v>
+        <v>1.84</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>1.84</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>1.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.66</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
@@ -2148,55 +2148,55 @@
         <v>1.16</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R7" t="n">
         <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Y7" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
         <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
         <v>26</v>
@@ -2205,7 +2205,7 @@
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2235,25 +2235,25 @@
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>25</v>
       </c>
       <c r="AR7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>9.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW7" t="n">
         <v>30</v>
@@ -2268,7 +2268,7 @@
         <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>18.5</v>
@@ -2280,7 +2280,7 @@
         <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
         <v>3.75</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
         <v>2.4</v>
@@ -2411,7 +2411,7 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
@@ -2483,7 +2483,7 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
         <v>15</v>
@@ -2498,7 +2498,7 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>13.5</v>
@@ -2525,16 +2525,16 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
         <v>2.22</v>
@@ -2656,7 +2656,7 @@
         <v>1.18</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
         <v>8</v>
@@ -2668,7 +2668,7 @@
         <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R9" t="n">
         <v>1.96</v>
@@ -2692,19 +2692,19 @@
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
         <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
@@ -2734,7 +2734,7 @@
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN9" t="n">
         <v>13</v>
@@ -2743,7 +2743,7 @@
         <v>8.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AQ9" t="n">
         <v>19</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2800,13 +2800,13 @@
         <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>7.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
         <v>5.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2919,7 +2919,7 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
         <v>1.71</v>
@@ -2940,7 +2940,7 @@
         <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2949,7 +2949,7 @@
         <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2958,16 +2958,16 @@
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>650</v>
+        <v>970</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
@@ -2976,13 +2976,13 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>610</v>
+        <v>890</v>
       </c>
       <c r="AJ10" t="n">
         <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL10" t="n">
         <v>34</v>
@@ -2994,16 +2994,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>530</v>
+        <v>730</v>
       </c>
       <c r="AP10" t="n">
         <v>18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS10" t="n">
         <v>40</v>
@@ -3018,7 +3018,7 @@
         <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3039,7 +3039,7 @@
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
         <v>34</v>
@@ -3048,7 +3048,7 @@
         <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O11" t="n">
         <v>1.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -3430,16 +3430,16 @@
         <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
         <v>1.96</v>
@@ -3463,7 +3463,7 @@
         <v>310</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
         <v>14</v>
@@ -3505,16 +3505,16 @@
         <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3523,10 +3523,10 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -3547,16 +3547,16 @@
         <v>11</v>
       </c>
       <c r="BD12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE12" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
         <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
@@ -3598,7 +3598,7 @@
         <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3753,7 +3753,7 @@
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO13" t="n">
         <v>150</v>
@@ -3765,10 +3765,10 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>8.199999999999999</v>
@@ -3777,10 +3777,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
         <v>8.199999999999999</v>
@@ -3792,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>10</v>
@@ -3801,7 +3801,7 @@
         <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
         <v>6.2</v>
@@ -3810,7 +3810,7 @@
         <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4</v>
@@ -3855,7 +3855,7 @@
         <v>6.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW13" t="n">
         <v>12.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I14" t="n">
         <v>1.61</v>
@@ -3920,28 +3920,28 @@
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
         <v>3.1</v>
@@ -3956,7 +3956,7 @@
         <v>2.62</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>21</v>
@@ -3974,19 +3974,19 @@
         <v>26</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
         <v>55</v>
       </c>
       <c r="AG14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -4010,7 +4010,7 @@
         <v>130</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP14" t="n">
         <v>15</v>
@@ -4019,25 +4019,25 @@
         <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
         <v>19</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -4046,22 +4046,22 @@
         <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC14" t="n">
-        <v>8</v>
-      </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
         <v>6.6</v>
@@ -4082,10 +4082,10 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
         <v>7.2</v>
@@ -4097,10 +4097,10 @@
         <v>12.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT14" t="n">
         <v>3.8</v>
@@ -4118,7 +4118,7 @@
         <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G15" t="n">
         <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="I15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J15" t="n">
         <v>3.85</v>
@@ -4177,7 +4177,7 @@
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -4186,40 +4186,40 @@
         <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
         <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
         <v>22</v>
@@ -4228,13 +4228,13 @@
         <v>20</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>42</v>
@@ -4246,7 +4246,7 @@
         <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
         <v>140</v>
@@ -4258,13 +4258,13 @@
         <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
         <v>80</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
@@ -4273,13 +4273,13 @@
         <v>8.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>7.8</v>
@@ -4291,7 +4291,7 @@
         <v>14</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
@@ -4300,22 +4300,22 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB15" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
         <v>8.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>4.7</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H16" t="n">
         <v>1.71</v>
@@ -4446,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>1.39</v>
@@ -4485,16 +4485,16 @@
         <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH16" t="n">
         <v>23</v>
@@ -4545,7 +4545,7 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY16" t="n">
         <v>14.5</v>
@@ -4554,22 +4554,22 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG16" t="n">
         <v>7.8</v>
@@ -4578,7 +4578,7 @@
         <v>3.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
         <v>1.87</v>
@@ -4676,7 +4676,7 @@
         <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
@@ -4691,22 +4691,22 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
         <v>1.64</v>
@@ -4715,7 +4715,7 @@
         <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
         <v>2.16</v>
@@ -4727,7 +4727,7 @@
         <v>26</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
         <v>130</v>
@@ -4748,7 +4748,7 @@
         <v>15.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>22</v>
@@ -4781,10 +4781,10 @@
         <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT17" t="n">
         <v>8.4</v>
@@ -4796,19 +4796,19 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
         <v>13.5</v>
@@ -4820,13 +4820,13 @@
         <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF17" t="n">
         <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH17" t="n">
         <v>4.3</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
         <v>1.72</v>
@@ -5029,7 +5029,7 @@
         <v>12.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.6</v>
@@ -5038,7 +5038,7 @@
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
         <v>13.5</v>
@@ -5050,13 +5050,13 @@
         <v>7.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>3.85</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>13</v>
@@ -5086,7 +5086,7 @@
         <v>3.85</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
         <v>2.84</v>
@@ -5199,7 +5199,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
         <v>1.38</v>
@@ -5223,10 +5223,10 @@
         <v>1.98</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.7</v>
@@ -5471,10 +5471,10 @@
         <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
@@ -5504,7 +5504,7 @@
         <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
         <v>16.5</v>
@@ -5516,7 +5516,7 @@
         <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ20" t="n">
         <v>32</v>
@@ -5546,7 +5546,7 @@
         <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -5573,7 +5573,7 @@
         <v>32</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BC20" t="n">
         <v>18</v>
@@ -5582,7 +5582,7 @@
         <v>4.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
         <v>11</v>
@@ -5600,34 +5600,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN20" t="n">
         <v>5.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP20" t="n">
         <v>16</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>26</v>
       </c>
       <c r="BS20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT20" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>7</v>
       </c>
       <c r="BU20" t="n">
         <v>5.3</v>
@@ -5636,13 +5636,13 @@
         <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
         <v>1.25</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G22" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="H22" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I22" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
         <v>4.6</v>
@@ -5961,34 +5961,34 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="O22" t="n">
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S22" t="n">
         <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U22" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
         <v>29</v>
@@ -6000,10 +6000,10 @@
         <v>28</v>
       </c>
       <c r="AA22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC22" t="n">
         <v>12.5</v>
@@ -6012,7 +6012,7 @@
         <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF22" t="n">
         <v>26</v>
@@ -6024,13 +6024,13 @@
         <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ22" t="n">
         <v>44</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -6039,128 +6039,128 @@
         <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC22" t="n">
         <v>17</v>
       </c>
-      <c r="AP22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4</v>
-      </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="BJ22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.7</v>
+        <v>1.08</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="BN22" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.95</v>
+        <v>1.08</v>
       </c>
       <c r="BP22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.6</v>
+        <v>1.08</v>
       </c>
       <c r="BR22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.2</v>
+        <v>1.08</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="BV22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW22" t="n">
-        <v>6.6</v>
+        <v>1.02</v>
       </c>
       <c r="BX22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.4</v>
+        <v>1.08</v>
       </c>
       <c r="BZ22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>6.2</v>
+        <v>1.08</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -6191,52 +6191,52 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G23" t="n">
         <v>4.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I23" t="n">
         <v>1.97</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="S23" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V23" t="n">
         <v>2.02</v>
@@ -6245,13 +6245,13 @@
         <v>1.31</v>
       </c>
       <c r="X23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>27</v>
@@ -6266,97 +6266,97 @@
         <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG23" t="n">
         <v>21</v>
       </c>
       <c r="AH23" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB23" t="n">
         <v>5.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD23" t="n">
         <v>4.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="BJ23" t="n">
         <v>8.800000000000001</v>
@@ -6377,13 +6377,13 @@
         <v>4.5</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS23" t="n">
         <v>7.2</v>
@@ -6392,7 +6392,7 @@
         <v>5.7</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BV23" t="n">
         <v>12.5</v>
@@ -6407,14 +6407,14 @@
         <v>6.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>3.8</v>
       </c>
       <c r="G24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -6466,10 +6466,10 @@
         <v>1.19</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.12</v>
@@ -6487,7 +6487,7 @@
         <v>1.89</v>
       </c>
       <c r="T24" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U24" t="n">
         <v>2.84</v>
@@ -6502,16 +6502,16 @@
         <v>46</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
         <v>19.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AC24" t="n">
         <v>14</v>
@@ -6523,7 +6523,7 @@
         <v>16.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
         <v>19.5</v>
@@ -6547,7 +6547,7 @@
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO24" t="n">
         <v>6.6</v>
@@ -6568,10 +6568,10 @@
         <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AW24" t="n">
         <v>13.5</v>
@@ -6583,13 +6583,13 @@
         <v>15.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BA24" t="n">
         <v>18.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -6601,16 +6601,16 @@
         <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
@@ -6646,7 +6646,7 @@
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="G25" t="n">
         <v>12.5</v>
@@ -6711,40 +6711,40 @@
         <v>1.4</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="K25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.13</v>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q25" t="n">
         <v>1.39</v>
       </c>
       <c r="R25" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="S25" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="T25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
         <v>3.45</v>
@@ -6813,25 +6813,25 @@
         <v>5</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS25" t="n">
         <v>4.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AU25" t="n">
         <v>5.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW25" t="n">
         <v>5.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>3.55</v>
       </c>
       <c r="AY25" t="n">
         <v>6.4</v>
@@ -6843,19 +6843,19 @@
         <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
         <v>7</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="BG25" t="n">
         <v>3.35</v>
@@ -6864,10 +6864,10 @@
         <v>5.6</v>
       </c>
       <c r="BI25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ25" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
         <v>5.3</v>
@@ -6879,7 +6879,7 @@
         <v>1.76</v>
       </c>
       <c r="BN25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
         <v>5.8</v>
@@ -6900,19 +6900,19 @@
         <v>4.5</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
@@ -6965,10 +6965,10 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
         <v>1.06</v>
@@ -6992,7 +6992,7 @@
         <v>1.08</v>
       </c>
       <c r="S26" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>
@@ -7213,16 +7213,16 @@
         <v>1.77</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.24</v>
@@ -7255,16 +7255,16 @@
         <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X27" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y27" t="n">
         <v>30</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>29</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -7279,10 +7279,10 @@
         <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="n">
         <v>15</v>
@@ -7294,10 +7294,10 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
         <v>19.5</v>
@@ -7312,61 +7312,61 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV27" t="n">
         <v>17.5</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="AZ27" t="n">
         <v>15</v>
       </c>
-      <c r="AW27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>13</v>
-      </c>
       <c r="BA27" t="n">
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
         <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH27" t="n">
         <v>4.5</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 09:14:46</t>
+          <t>2026-07-02 11:28:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -863,7 +863,7 @@
         <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
         <v>2.86</v>
@@ -875,7 +875,7 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -887,25 +887,25 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
         <v>1.63</v>
@@ -914,16 +914,16 @@
         <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
         <v>9.4</v>
@@ -932,10 +932,10 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
         <v>14.5</v>
@@ -944,16 +944,16 @@
         <v>14</v>
       </c>
       <c r="AI2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK2" t="n">
         <v>30</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>27</v>
-      </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>150</v>
@@ -968,10 +968,10 @@
         <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AS2" t="n">
         <v>25</v>
@@ -980,13 +980,13 @@
         <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -995,13 +995,13 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>19.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
@@ -1010,7 +1010,7 @@
         <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK3" t="n">
         <v>22</v>
       </c>
-      <c r="AK3" t="n">
-        <v>24</v>
-      </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO3" t="n">
         <v>2.9</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>2.98</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1374,13 +1374,13 @@
         <v>1.56</v>
       </c>
       <c r="I4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.17</v>
@@ -1398,28 +1398,28 @@
         <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1446,7 +1446,7 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
@@ -1458,10 +1458,10 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
         <v>85</v>
@@ -1473,7 +1473,7 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.45</v>
@@ -1482,16 +1482,16 @@
         <v>3.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AW4" t="n">
         <v>3.75</v>
@@ -1503,22 +1503,22 @@
         <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
         <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
         <v>4.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.21</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>1.66</v>
+        <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.49</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.88</v>
       </c>
       <c r="S5" t="n">
-        <v>1.21</v>
+        <v>1.89</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -1876,52 +1876,52 @@
         <v>5.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I6" t="n">
         <v>1.64</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1951,16 +1951,16 @@
         <v>970</v>
       </c>
       <c r="AF6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH6" t="n">
         <v>29</v>
       </c>
-      <c r="AH6" t="n">
-        <v>27</v>
-      </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1981,58 +1981,58 @@
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AR6" t="n">
         <v>3.65</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AV6" t="n">
         <v>4</v>
       </c>
       <c r="AW6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.84</v>
+        <v>3.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.16</v>
@@ -2151,82 +2151,82 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
         <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Y7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AC7" t="n">
         <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL7" t="n">
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN7" t="n">
         <v>5</v>
@@ -2235,25 +2235,25 @@
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
         <v>30</v>
@@ -2265,7 +2265,7 @@
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
         <v>25</v>
@@ -2280,25 +2280,25 @@
         <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
         <v>16.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2313,22 +2313,22 @@
         <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS7" t="n">
         <v>6.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2337,10 +2337,10 @@
         <v>7.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.9</v>
@@ -2411,40 +2411,40 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
         <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="n">
         <v>20</v>
@@ -2453,16 +2453,16 @@
         <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF8" t="n">
         <v>26</v>
       </c>
       <c r="AG8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>16.5</v>
@@ -2471,22 +2471,22 @@
         <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP8" t="n">
         <v>19.5</v>
@@ -2498,13 +2498,13 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT8" t="n">
         <v>13.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2525,22 +2525,22 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2567,7 +2567,7 @@
         <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
         <v>8.199999999999999</v>
@@ -2585,10 +2585,10 @@
         <v>4.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>23</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2647,10 +2647,10 @@
         <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.18</v>
@@ -2671,7 +2671,7 @@
         <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
         <v>1.9</v>
@@ -2686,7 +2686,7 @@
         <v>1.76</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2734,13 +2734,13 @@
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AN9" t="n">
         <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP9" t="n">
         <v>30</v>
@@ -2767,7 +2767,7 @@
         <v>17.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY9" t="n">
         <v>12.5</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2922,7 +2922,7 @@
         <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.53</v>
@@ -2931,7 +2931,7 @@
         <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
         <v>2.3</v>
@@ -2940,7 +2940,7 @@
         <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2964,7 +2964,7 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
@@ -2976,7 +2976,7 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="AJ10" t="n">
         <v>18</v>
@@ -2994,7 +2994,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>730</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
         <v>18</v>
@@ -3003,7 +3003,7 @@
         <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AS10" t="n">
         <v>40</v>
@@ -3048,7 +3048,7 @@
         <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.32</v>
@@ -3454,7 +3454,7 @@
         <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
         <v>90</v>
@@ -3505,16 +3505,16 @@
         <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3523,10 +3523,10 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -3547,16 +3547,16 @@
         <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
         <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3642,37 +3642,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>4.7</v>
@@ -3684,197 +3684,197 @@
         <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK13" t="n">
         <v>25</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AL13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO13" t="n">
         <v>32</v>
       </c>
-      <c r="Z13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AP13" t="n">
         <v>17.5</v>
       </c>
-      <c r="AL13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BH13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI13" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BT13" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="BX13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.4</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.57</v>
+        <v>7.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.61</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
         <v>4.7</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
         <v>1.99</v>
       </c>
       <c r="V14" t="n">
-        <v>2.62</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.5</v>
+        <v>270</v>
       </c>
       <c r="AB14" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AE14" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>55</v>
+        <v>9.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
-        <v>110</v>
+        <v>17.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
         <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>130</v>
+        <v>6.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>9.800000000000001</v>
+        <v>150</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AZ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="CA14" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="I15" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AB15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
         <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AG15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY15" t="n">
         <v>21</v>
       </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="AZ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB15" t="n">
         <v>5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BX15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
         <v>2.06</v>
@@ -4485,22 +4485,22 @@
         <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
         <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH16" t="n">
         <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
         <v>150</v>
@@ -4515,7 +4515,7 @@
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
         <v>13</v>
@@ -4545,7 +4545,7 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
         <v>14.5</v>
@@ -4554,22 +4554,22 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
         <v>7.8</v>
@@ -4578,7 +4578,7 @@
         <v>3.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4614,13 +4614,13 @@
         <v>4.7</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BV16" t="n">
         <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BX16" t="n">
         <v>27</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.53</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
         <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>8.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP17" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF17" t="n">
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BT17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BG17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU17" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H18" t="n">
         <v>4.4</v>
       </c>
-      <c r="G18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.78</v>
-      </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="X18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Y18" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC18" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AD18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
         <v>15</v>
       </c>
-      <c r="AA18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AG18" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>23</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="BA18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB18" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4</v>
-      </c>
       <c r="BC18" t="n">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
         <v>4</v>
       </c>
       <c r="BF18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG18" t="n">
         <v>3.95</v>
       </c>
-      <c r="BG18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH18" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP18" t="n">
         <v>12</v>
       </c>
-      <c r="BN18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ18" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BT18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU18" t="n">
         <v>4.7</v>
       </c>
-      <c r="BU18" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5166,229 +5166,229 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR19" t="n">
         <v>9</v>
       </c>
-      <c r="AD19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AS19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX19" t="n">
         <v>4</v>
       </c>
-      <c r="AT19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH19" t="n">
         <v>3.85</v>
       </c>
-      <c r="BG19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU19" t="n">
         <v>3.6</v>
       </c>
-      <c r="BT19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5415,234 +5415,234 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="G20" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
         <v>4.1</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BN20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT20" t="n">
         <v>4.7</v>
       </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR20" t="n">
+      <c r="BU20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX20" t="n">
         <v>26</v>
       </c>
-      <c r="BS20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT20" t="n">
+      <c r="BY20" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -5940,10 +5940,10 @@
         <v>2.48</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H22" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I22" t="n">
         <v>2.82</v>
@@ -5976,25 +5976,25 @@
         <v>1.67</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T22" t="n">
         <v>1.47</v>
       </c>
       <c r="U22" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V22" t="n">
         <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z22" t="n">
         <v>28</v>
@@ -6003,22 +6003,22 @@
         <v>46</v>
       </c>
       <c r="AB22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD22" t="n">
         <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AF22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
         <v>17.5</v>
@@ -6027,34 +6027,34 @@
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL22" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
         <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO22" t="n">
         <v>16</v>
       </c>
       <c r="AP22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>13</v>
@@ -6066,7 +6066,7 @@
         <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AX22" t="n">
         <v>16</v>
@@ -6075,92 +6075,92 @@
         <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
         <v>17</v>
       </c>
       <c r="BD22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF22" t="n">
         <v>9.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.08</v>
+        <v>3.65</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.08</v>
+        <v>4.8</v>
       </c>
       <c r="BL22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.08</v>
+        <v>4.7</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.08</v>
+        <v>6.6</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.08</v>
+        <v>7.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.08</v>
+        <v>4.8</v>
       </c>
       <c r="BV22" t="n">
         <v>18</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.08</v>
+        <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.08</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
         <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R23" t="n">
         <v>1.89</v>
@@ -6233,7 +6233,7 @@
         <v>1.96</v>
       </c>
       <c r="T23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
         <v>2.88</v>
@@ -6254,37 +6254,37 @@
         <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB23" t="n">
         <v>32</v>
       </c>
       <c r="AC23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
         <v>19</v>
       </c>
       <c r="AF23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL23" t="n">
         <v>40</v>
@@ -6293,13 +6293,13 @@
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
         <v>7.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ23" t="n">
         <v>14</v>
@@ -6311,19 +6311,19 @@
         <v>18</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
         <v>12.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
@@ -6335,22 +6335,22 @@
         <v>16.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BF23" t="n">
         <v>15</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="BH23" t="n">
         <v>5.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G24" t="n">
         <v>4.5</v>
@@ -6454,10 +6454,10 @@
         <v>1.76</v>
       </c>
       <c r="I24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="J24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
         <v>5</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.12</v>
@@ -6481,7 +6481,7 @@
         <v>1.35</v>
       </c>
       <c r="R24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
         <v>1.89</v>
@@ -6493,7 +6493,7 @@
         <v>2.84</v>
       </c>
       <c r="V24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W24" t="n">
         <v>1.3</v>
@@ -6502,10 +6502,10 @@
         <v>46</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
         <v>26</v>
@@ -6517,13 +6517,13 @@
         <v>14</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>16.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG24" t="n">
         <v>19.5</v>
@@ -6550,7 +6550,7 @@
         <v>24</v>
       </c>
       <c r="AO24" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP24" t="n">
         <v>29</v>
@@ -6568,13 +6568,13 @@
         <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW24" t="n">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX24" t="n">
         <v>34</v>
@@ -6583,13 +6583,13 @@
         <v>15.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
         <v>18.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -6601,7 +6601,7 @@
         <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG24" t="n">
         <v>3.55</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -6732,13 +6732,13 @@
         <v>3.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="R25" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="S25" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T25" t="n">
         <v>1.7</v>
@@ -6759,10 +6759,10 @@
         <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA25" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AB25" t="n">
         <v>55</v>
@@ -6771,10 +6771,10 @@
         <v>970</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE25" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AF25" t="n">
         <v>110</v>
@@ -6783,10 +6783,10 @@
         <v>42</v>
       </c>
       <c r="AH25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -6804,61 +6804,61 @@
         <v>120</v>
       </c>
       <c r="AO25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AP25" t="n">
         <v>4</v>
       </c>
-      <c r="AP25" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AR25" t="n">
         <v>8.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AT25" t="n">
         <v>30</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AV25" t="n">
         <v>8.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BH25" t="n">
         <v>5.6</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.06</v>
@@ -7001,7 +7001,7 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>
@@ -7210,61 +7210,61 @@
         <v>1.63</v>
       </c>
       <c r="G27" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H27" t="n">
         <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R27" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
         <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X27" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -7273,19 +7273,19 @@
         <v>140</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD27" t="n">
         <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
         <v>12.5</v>
@@ -7294,31 +7294,31 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
         <v>19.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO27" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP27" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR27" t="n">
         <v>1.03</v>
@@ -7327,10 +7327,10 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
         <v>17.5</v>
@@ -7339,40 +7339,40 @@
         <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA27" t="n">
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE27" t="n">
         <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.6</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
@@ -7396,13 +7396,13 @@
         <v>11</v>
       </c>
       <c r="BQ27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BT27" t="n">
         <v>9.199999999999999</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
         <v>27</v>
       </c>
-      <c r="BX27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>28</v>
-      </c>
       <c r="BZ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 11:28:14</t>
+          <t>2026-07-02 13:44:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
         <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
         <v>2.86</v>
@@ -875,94 +875,94 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U2" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
         <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI2" t="n">
         <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
         <v>19.5</v>
@@ -971,25 +971,25 @@
         <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
         <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
         <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,16 +998,16 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="n">
         <v>26</v>
@@ -1022,7 +1022,7 @@
         <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
         <v>7.6</v>
@@ -1126,7 +1126,7 @@
         <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -1135,28 +1135,28 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
         <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
@@ -1180,7 +1180,7 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>110</v>
@@ -1204,7 +1204,7 @@
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>40</v>
@@ -1216,64 +1216,64 @@
         <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="BC3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="BE3" t="n">
         <v>3.6</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BF3" t="n">
         <v>4</v>
       </c>
-      <c r="AV3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI3" t="n">
         <v>2.94</v>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
         <v>4.8</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>5.9</v>
@@ -1410,7 +1410,7 @@
         <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
         <v>2.4</v>
@@ -1458,7 +1458,7 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
         <v>70</v>
@@ -1473,28 +1473,28 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AS4" t="n">
         <v>3.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AX4" t="n">
         <v>4.1</v>
@@ -1503,13 +1503,13 @@
         <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
         <v>4.1</v>
@@ -1518,7 +1518,7 @@
         <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
         <v>4.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1649,13 @@
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
         <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S5" t="n">
         <v>1.89</v>
@@ -1685,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>26</v>
@@ -1700,7 +1700,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>48</v>
@@ -1709,10 +1709,10 @@
         <v>250</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
         <v>50</v>
@@ -1727,28 +1727,28 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1757,10 +1757,10 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.56</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BB5" t="n">
         <v>4.4</v>
@@ -1769,34 +1769,34 @@
         <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.56</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BF5" t="n">
         <v>2.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>4.1</v>
@@ -1814,25 +1814,25 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J6" t="n">
         <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1906,7 +1906,7 @@
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
@@ -1921,7 +1921,7 @@
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1984,19 +1984,19 @@
         <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AS6" t="n">
         <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AV6" t="n">
         <v>4</v>
@@ -2011,7 +2011,7 @@
         <v>3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA6" t="n">
         <v>3.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
@@ -2142,7 +2142,7 @@
         <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>1.16</v>
@@ -2151,19 +2151,19 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.11</v>
       </c>
       <c r="P7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>1.36</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
         <v>1.81</v>
@@ -2172,13 +2172,13 @@
         <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
         <v>44</v>
@@ -2226,7 +2226,7 @@
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN7" t="n">
         <v>5</v>
@@ -2238,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
         <v>36</v>
@@ -2247,7 +2247,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
         <v>10.5</v>
@@ -2280,7 +2280,7 @@
         <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
@@ -2289,10 +2289,10 @@
         <v>16.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
@@ -2319,7 +2319,7 @@
         <v>5.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BS7" t="n">
         <v>6.2</v>
@@ -2334,13 +2334,13 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY7" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I8" t="n">
         <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
@@ -2420,7 +2420,7 @@
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
         <v>1.52</v>
@@ -2429,16 +2429,16 @@
         <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
         <v>23</v>
@@ -2525,7 +2525,7 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
@@ -2558,19 +2558,19 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
@@ -2582,7 +2582,7 @@
         <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
         <v>17</v>
@@ -2591,10 +2591,10 @@
         <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
         <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.18</v>
@@ -2659,13 +2659,13 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
         <v>1.37</v>
@@ -2674,25 +2674,25 @@
         <v>1.97</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
@@ -2728,7 +2728,7 @@
         <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
         <v>28</v>
@@ -2737,7 +2737,7 @@
         <v>44</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
         <v>9.4</v>
@@ -2764,10 +2764,10 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY9" t="n">
         <v>12.5</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2919,22 +2919,22 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>1.22</v>
@@ -2946,7 +2946,7 @@
         <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>120</v>
@@ -2964,22 +2964,22 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>990</v>
+        <v>530</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK10" t="n">
         <v>16.5</v>
@@ -2997,7 +2997,7 @@
         <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>20</v>
@@ -3012,31 +3012,31 @@
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
         <v>19.5</v>
@@ -3045,10 +3045,10 @@
         <v>34</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
@@ -3060,13 +3060,13 @@
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.6</v>
@@ -3075,7 +3075,7 @@
         <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.6</v>
@@ -3084,35 +3084,35 @@
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
         <v>38</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10" t="n">
         <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3143,112 +3143,112 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>2.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP11" t="n">
         <v>1.03</v>
@@ -3299,74 +3299,74 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM11" t="n">
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
         <v>1.45</v>
@@ -3418,7 +3418,7 @@
         <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>4.9</v>
@@ -3451,7 +3451,7 @@
         <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>38</v>
@@ -3466,7 +3466,7 @@
         <v>11.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
         <v>38</v>
@@ -3475,22 +3475,22 @@
         <v>150</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL12" t="n">
         <v>42</v>
@@ -3505,16 +3505,16 @@
         <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3523,10 +3523,10 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -3547,16 +3547,16 @@
         <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF12" t="n">
         <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>110</v>
@@ -4019,10 +4019,10 @@
         <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -4031,10 +4031,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -4055,16 +4055,16 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
         <v>5.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="n">
         <v>4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>6.4</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I15" t="n">
         <v>1.61</v>
@@ -4180,7 +4180,7 @@
         <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
         <v>4.2</v>
@@ -4192,34 +4192,34 @@
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
         <v>2.62</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA15" t="n">
         <v>17</v>
@@ -4231,7 +4231,7 @@
         <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE15" t="n">
         <v>19</v>
@@ -4291,7 +4291,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AY15" t="n">
         <v>21</v>
@@ -4300,22 +4300,22 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG15" t="n">
         <v>7.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>1.71</v>
       </c>
       <c r="I16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J16" t="n">
         <v>3.75</v>
@@ -4446,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.39</v>
@@ -4455,13 +4455,13 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
         <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
         <v>1.21</v>
@@ -4518,7 +4518,7 @@
         <v>75</v>
       </c>
       <c r="AO16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
@@ -4545,7 +4545,7 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
         <v>14.5</v>
@@ -4554,22 +4554,22 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG16" t="n">
         <v>7.8</v>
@@ -4584,34 +4584,34 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BP16" t="n">
         <v>44</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU16" t="n">
         <v>3.45</v>
@@ -4620,13 +4620,13 @@
         <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX16" t="n">
         <v>27</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
         <v>2.88</v>
@@ -4682,10 +4682,10 @@
         <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -4706,13 +4706,13 @@
         <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V17" t="n">
         <v>1.43</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.7</v>
       </c>
       <c r="G18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
         <v>4.4</v>
@@ -4951,7 +4951,7 @@
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
         <v>1.62</v>
@@ -4960,7 +4960,7 @@
         <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
         <v>1.64</v>
@@ -4972,7 +4972,7 @@
         <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X18" t="n">
         <v>27</v>
@@ -4996,7 +4996,7 @@
         <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
@@ -5062,7 +5062,7 @@
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.29</v>
@@ -5202,7 +5202,7 @@
         <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
         <v>2.12</v>
@@ -5211,16 +5211,16 @@
         <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
         <v>2.1</v>
@@ -5229,7 +5229,7 @@
         <v>1.24</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>13</v>
       </c>
       <c r="AX19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
@@ -5334,10 +5334,10 @@
         <v>38</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI19" t="n">
         <v>3</v>
@@ -5346,16 +5346,16 @@
         <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO19" t="n">
         <v>6</v>
@@ -5364,13 +5364,13 @@
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT19" t="n">
         <v>4.7</v>
@@ -5382,13 +5382,13 @@
         <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5441,16 +5441,16 @@
         <v>1.83</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
         <v>4.1</v>
@@ -5462,7 +5462,7 @@
         <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
         <v>1.41</v>
@@ -5480,40 +5480,40 @@
         <v>2.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
         <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
         <v>9.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>22</v>
       </c>
       <c r="AF20" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -5534,7 +5534,7 @@
         <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP20" t="n">
         <v>13</v>
@@ -5561,7 +5561,7 @@
         <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
@@ -5570,22 +5570,22 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
         <v>8.800000000000001</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
         <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX22" t="n">
         <v>16</v>
@@ -6090,7 +6090,7 @@
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.1</v>
+        <v>38</v>
       </c>
       <c r="BF22" t="n">
         <v>9.4</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G24" t="n">
         <v>4.5</v>
@@ -6454,7 +6454,7 @@
         <v>1.76</v>
       </c>
       <c r="I24" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J24" t="n">
         <v>4.7</v>
@@ -6481,7 +6481,7 @@
         <v>1.35</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S24" t="n">
         <v>1.89</v>
@@ -6493,7 +6493,7 @@
         <v>2.84</v>
       </c>
       <c r="V24" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W24" t="n">
         <v>1.3</v>
@@ -6571,10 +6571,10 @@
         <v>4.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX24" t="n">
         <v>34</v>
@@ -6604,7 +6604,7 @@
         <v>5.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.13</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O26" t="n">
         <v>1.06</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
         <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
         <v>2.86</v>
@@ -887,10 +887,10 @@
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.73</v>
@@ -917,7 +917,7 @@
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -944,7 +944,7 @@
         <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>65</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.36</v>
@@ -1135,206 +1135,206 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>970</v>
-      </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP3" t="n">
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
         <v>3.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.75</v>
+        <v>8.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.67</v>
+        <v>6.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.69</v>
+        <v>7.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.73</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.34</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
         <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1428,13 +1428,13 @@
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1443,85 +1443,85 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO4" t="n">
         <v>29</v>
       </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>970</v>
-      </c>
       <c r="AP4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR4" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AS4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA4" t="n">
         <v>3.6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BB4" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BG4" t="n">
         <v>4.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
@@ -1631,7 +1631,7 @@
         <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K5" t="n">
         <v>10.5</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.12</v>
@@ -1652,13 +1652,13 @@
         <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R5" t="n">
         <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T5" t="n">
         <v>2.1</v>
@@ -1697,7 +1697,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1727,28 +1727,28 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.77</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1760,7 +1760,7 @@
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
         <v>4.4</v>
@@ -1772,13 +1772,13 @@
         <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="BF5" t="n">
         <v>2.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>5.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.55</v>
@@ -1888,7 +1888,7 @@
         <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1897,7 +1897,7 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
@@ -1918,7 +1918,7 @@
         <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
         <v>2.52</v>
@@ -1930,109 +1930,109 @@
         <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
         <v>970</v>
       </c>
       <c r="AF6" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
         <v>29</v>
       </c>
-      <c r="AI6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>970</v>
-      </c>
       <c r="AP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.6</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -2151,7 +2151,7 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1.11</v>
@@ -2160,10 +2160,10 @@
         <v>3.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
         <v>1.81</v>
@@ -2172,25 +2172,25 @@
         <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
         <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB7" t="n">
         <v>19.5</v>
@@ -2202,7 +2202,7 @@
         <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
         <v>17</v>
@@ -2211,49 +2211,49 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
         <v>16</v>
       </c>
       <c r="AL7" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
         <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AU7" t="n">
         <v>10.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW7" t="n">
         <v>30</v>
@@ -2271,7 +2271,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -2280,13 +2280,13 @@
         <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BH7" t="n">
         <v>6.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
         <v>2.76</v>
@@ -2420,7 +2420,7 @@
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
         <v>1.52</v>
@@ -2429,7 +2429,7 @@
         <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
         <v>1.56</v>
@@ -2462,7 +2462,7 @@
         <v>26</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>16.5</v>
@@ -2477,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
         <v>55</v>
@@ -2498,7 +2498,7 @@
         <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="AT8" t="n">
         <v>13.5</v>
@@ -2525,16 +2525,16 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
         <v>2.24</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
@@ -2686,7 +2686,7 @@
         <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2701,7 +2701,7 @@
         <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2731,10 +2731,10 @@
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN9" t="n">
         <v>12.5</v>
@@ -2743,7 +2743,7 @@
         <v>9.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
         <v>19</v>
@@ -2764,13 +2764,13 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
         <v>27</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>12</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H10" t="n">
         <v>5.2</v>
@@ -2976,7 +2976,7 @@
         <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AJ10" t="n">
         <v>17.5</v>
@@ -2988,7 +2988,7 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
         <v>8.199999999999999</v>
@@ -3024,7 +3024,7 @@
         <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
         <v>2.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R11" t="n">
         <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
         <v>1.42</v>
@@ -3191,10 +3191,10 @@
         <v>2.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X11" t="n">
         <v>36</v>
@@ -3203,28 +3203,28 @@
         <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC11" t="n">
         <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
         <v>16</v>
@@ -3233,10 +3233,10 @@
         <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -3245,128 +3245,128 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BH11" t="n">
         <v>5.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BL11" t="n">
         <v>70</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>15</v>
+        <v>5.2</v>
       </c>
       <c r="BR11" t="n">
         <v>27</v>
       </c>
       <c r="BS11" t="n">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>14.5</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>14</v>
-      </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>1.45</v>
       </c>
       <c r="H12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K12" t="n">
         <v>5.3</v>
@@ -3418,7 +3418,7 @@
         <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
         <v>4.9</v>
@@ -3430,16 +3430,16 @@
         <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
         <v>1.96</v>
@@ -3451,13 +3451,13 @@
         <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
         <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="AA12" t="n">
         <v>310</v>
@@ -3472,7 +3472,7 @@
         <v>38</v>
       </c>
       <c r="AE12" t="n">
-        <v>150</v>
+        <v>480</v>
       </c>
       <c r="AF12" t="n">
         <v>9.800000000000001</v>
@@ -3484,7 +3484,7 @@
         <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AJ12" t="n">
         <v>13</v>
@@ -3496,7 +3496,7 @@
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="AN12" t="n">
         <v>7.2</v>
@@ -3505,28 +3505,28 @@
         <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -3547,16 +3547,16 @@
         <v>11</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -3657,16 +3657,16 @@
         <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3693,10 +3693,10 @@
         <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
         <v>1.4</v>
@@ -3705,55 +3705,55 @@
         <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>440</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
         <v>36</v>
       </c>
       <c r="AM13" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AO13" t="n">
         <v>32</v>
@@ -3768,7 +3768,7 @@
         <v>19.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
@@ -3780,7 +3780,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3792,19 +3792,19 @@
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
         <v>11</v>
@@ -3822,19 +3822,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN13" t="n">
         <v>5.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP13" t="n">
         <v>16</v>
@@ -3858,10 +3858,10 @@
         <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY13" t="n">
         <v>7.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.69</v>
@@ -3944,7 +3944,7 @@
         <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T14" t="n">
         <v>1.9</v>
@@ -3965,7 +3965,7 @@
         <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>70</v>
+        <v>540</v>
       </c>
       <c r="AA14" t="n">
         <v>270</v>
@@ -3986,13 +3986,13 @@
         <v>9.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ14" t="n">
         <v>15</v>
@@ -4004,7 +4004,7 @@
         <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>390</v>
       </c>
       <c r="AN14" t="n">
         <v>6.6</v>
@@ -4019,10 +4019,10 @@
         <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -4031,10 +4031,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -4055,16 +4055,16 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
         <v>5.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="n">
         <v>4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -4165,22 +4165,22 @@
         <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
         <v>4.2</v>
@@ -4189,10 +4189,10 @@
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -4201,19 +4201,19 @@
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V15" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
         <v>8.800000000000001</v>
@@ -4249,7 +4249,7 @@
         <v>36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AK15" t="n">
         <v>120</v>
@@ -4261,7 +4261,7 @@
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
         <v>9.800000000000001</v>
@@ -4291,7 +4291,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY15" t="n">
         <v>21</v>
@@ -4300,22 +4300,22 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC15" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG15" t="n">
         <v>7.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -4404,229 +4404,229 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="G16" t="n">
-        <v>5.8</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
-        <v>1.71</v>
+        <v>2.86</v>
       </c>
       <c r="I16" t="n">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.27</v>
       </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY16" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU16" t="n">
         <v>4.5</v>
       </c>
-      <c r="BD16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU16" t="n">
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>3.45</v>
       </c>
-      <c r="BV16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BX16" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.4</v>
+        <v>2.22</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -4658,230 +4658,230 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>1.73</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
         <v>4</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T17" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="AO17" t="n">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="BT17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>5.7</v>
       </c>
-      <c r="BO17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
+      <c r="BX17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY17" t="n">
         <v>7.4</v>
       </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BZ17" t="n">
         <v>0</v>
       </c>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G18" t="n">
         <v>1.83</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
         <v>5.3</v>
@@ -4951,7 +4951,7 @@
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>1.62</v>
@@ -4966,7 +4966,7 @@
         <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
@@ -4978,13 +4978,13 @@
         <v>27</v>
       </c>
       <c r="Y18" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="Z18" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>14</v>
@@ -4996,19 +4996,19 @@
         <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ18" t="n">
         <v>23</v>
@@ -5017,70 +5017,70 @@
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BC18" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="n">
         <v>4.3</v>
@@ -5092,7 +5092,7 @@
         <v>9.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -5178,13 +5178,13 @@
         <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J19" t="n">
         <v>3.85</v>
@@ -5205,10 +5205,10 @@
         <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
         <v>1.45</v>
@@ -5226,13 +5226,13 @@
         <v>2.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
         <v>15</v>
@@ -5253,7 +5253,7 @@
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AG19" t="n">
         <v>23</v>
@@ -5265,82 +5265,82 @@
         <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
         <v>12.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV19" t="n">
         <v>9</v>
       </c>
-      <c r="AS19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AW19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF19" t="n">
-        <v>38</v>
-      </c>
       <c r="BG19" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="n">
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -5432,10 +5432,10 @@
         <v>4.9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I20" t="n">
         <v>1.83</v>
@@ -5447,7 +5447,7 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5465,7 +5465,7 @@
         <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
         <v>3.1</v>
@@ -5477,7 +5477,7 @@
         <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W20" t="n">
         <v>1.23</v>
@@ -5504,7 +5504,7 @@
         <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AF20" t="n">
         <v>42</v>
@@ -5519,19 +5519,19 @@
         <v>36</v>
       </c>
       <c r="AJ20" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
         <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="n">
         <v>11</v>
@@ -5561,7 +5561,7 @@
         <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
@@ -5570,22 +5570,22 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
         <v>8.800000000000001</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>5.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="S21" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="G22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.78</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.72</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y22" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG22" t="n">
         <v>19</v>
       </c>
-      <c r="Z22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>470</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC22" t="n">
         <v>16</v>
       </c>
-      <c r="AE22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="BD22" t="n">
         <v>16</v>
       </c>
-      <c r="AH22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI22" t="n">
+      <c r="BE22" t="n">
         <v>34</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>38</v>
-      </c>
       <c r="BF22" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BJ22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP22" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
         <v>7.4</v>
       </c>
       <c r="BT22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BY22" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>24</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BZ22" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -6182,239 +6182,239 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I23" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R23" t="n">
         <v>1.89</v>
       </c>
       <c r="S23" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V23" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB23" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AC23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG23" t="n">
         <v>19</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>22</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
       </c>
       <c r="AI23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT23" t="n">
         <v>25</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL23" t="n">
+      <c r="AU23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE23" t="n">
         <v>40</v>
       </c>
-      <c r="AM23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>34</v>
-      </c>
       <c r="BF23" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BJ23" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
         <v>4.3</v>
       </c>
       <c r="BV23" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -6436,246 +6436,246 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="G24" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.76</v>
+        <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R24" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S24" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="T24" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="U24" t="n">
-        <v>2.84</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="Y24" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA24" t="n">
         <v>970</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC24" t="n">
         <v>970</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>540</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT24" t="n">
         <v>26</v>
       </c>
-      <c r="AB24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>25</v>
-      </c>
       <c r="AU24" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV24" t="n">
         <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BD24" t="n">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BF24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH24" t="n">
         <v>5.6</v>
       </c>
-      <c r="BG24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI24" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,246 +6690,246 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="G25" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="J25" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="K25" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
         <v>1.02</v>
       </c>
-      <c r="N25" t="n">
-        <v>6.8</v>
-      </c>
       <c r="O25" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="R25" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="S25" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="V25" t="n">
-        <v>3.45</v>
+        <v>2.46</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="Y25" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH25" t="n">
         <v>970</v>
       </c>
-      <c r="Z25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>29</v>
-      </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK25" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AL25" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN25" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AO25" t="n">
         <v>4.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
         <v>5.6</v>
       </c>
-      <c r="BI25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BU25" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,239 +6944,239 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="H26" t="n">
-        <v>1.35</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J26" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P26" t="n">
-        <v>1.08</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="R26" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="S26" t="n">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>
@@ -7228,28 +7228,28 @@
         <v>1.27</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N27" t="n">
         <v>5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R27" t="n">
         <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
         <v>2.32</v>
@@ -7261,10 +7261,10 @@
         <v>2.32</v>
       </c>
       <c r="X27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -7273,10 +7273,10 @@
         <v>140</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
         <v>26</v>
@@ -7285,7 +7285,7 @@
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
         <v>12.5</v>
@@ -7297,7 +7297,7 @@
         <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
         <v>19.5</v>
@@ -7430,7 +7430,261 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 15:58:36</t>
+          <t>2026-07-02 18:12:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>22</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-07-02 18:12:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -860,13 +860,13 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
         <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J2" t="n">
         <v>3.9</v>
@@ -884,25 +884,25 @@
         <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
         <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
         <v>1.48</v>
       </c>
       <c r="U2" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
@@ -914,19 +914,19 @@
         <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -935,13 +935,13 @@
         <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
         <v>46</v>
@@ -950,10 +950,10 @@
         <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
@@ -965,16 +965,16 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
         <v>15.5</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX2" t="n">
         <v>17</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -1001,16 +1001,16 @@
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
         <v>6.6</v>
@@ -1156,7 +1156,7 @@
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.18</v>
@@ -1183,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AE3" t="n">
         <v>700</v>
@@ -1201,7 +1201,7 @@
         <v>700</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
         <v>46</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
         <v>120</v>
@@ -1228,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>5.1</v>
@@ -1252,25 +1252,25 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
         <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
         <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.75</v>
@@ -1294,7 +1294,7 @@
         <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="I4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1404,19 +1404,19 @@
         <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>2.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
@@ -1449,7 +1449,7 @@
         <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1473,58 +1473,58 @@
         <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.65</v>
+        <v>2.06</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.65</v>
+        <v>2.04</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>7.4</v>
@@ -1745,7 +1745,7 @@
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1778,7 +1778,7 @@
         <v>2.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1906,7 +1906,7 @@
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
@@ -1936,7 +1936,7 @@
         <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
@@ -1948,7 +1948,7 @@
         <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
         <v>500</v>
@@ -2008,13 +2008,13 @@
         <v>4.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
@@ -2026,7 +2026,7 @@
         <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="BF6" t="n">
         <v>4.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.5</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -2151,7 +2151,7 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.11</v>
@@ -2160,25 +2160,25 @@
         <v>3.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="T7" t="n">
         <v>1.45</v>
       </c>
       <c r="U7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
         <v>500</v>
@@ -2187,7 +2187,7 @@
         <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AA7" t="n">
         <v>700</v>
@@ -2199,7 +2199,7 @@
         <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AE7" t="n">
         <v>700</v>
@@ -2214,7 +2214,7 @@
         <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -2226,25 +2226,25 @@
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO7" t="n">
         <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
         <v>16</v>
@@ -2280,7 +2280,7 @@
         <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
@@ -2298,28 +2298,28 @@
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN7" t="n">
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP7" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS7" t="n">
         <v>6.2</v>
@@ -2328,7 +2328,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,7 +2340,7 @@
         <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.54</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
@@ -2429,7 +2429,7 @@
         <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
         <v>1.56</v>
@@ -2444,7 +2444,7 @@
         <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
         <v>20</v>
@@ -2462,7 +2462,7 @@
         <v>26</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>16.5</v>
@@ -2471,13 +2471,13 @@
         <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>55</v>
@@ -2525,7 +2525,7 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
@@ -2534,7 +2534,7 @@
         <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
@@ -2552,7 +2552,7 @@
         <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,40 +2561,40 @@
         <v>12</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
         <v>2.24</v>
@@ -2683,10 +2683,10 @@
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2743,7 +2743,7 @@
         <v>9.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>19</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
         <v>5.2</v>
@@ -2919,7 +2919,7 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
         <v>1.67</v>
@@ -2931,7 +2931,7 @@
         <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
         <v>2.34</v>
@@ -2940,7 +2940,7 @@
         <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2949,10 +2949,10 @@
         <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB10" t="n">
         <v>11</v>
@@ -2961,10 +2961,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>530</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2973,10 +2973,10 @@
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
         <v>17.5</v>
@@ -2988,7 +2988,7 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="AN10" t="n">
         <v>8.199999999999999</v>
@@ -3012,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10" t="n">
         <v>17.5</v>
@@ -3024,10 +3024,10 @@
         <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -3039,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE10" t="n">
         <v>34</v>
@@ -3072,7 +3072,7 @@
         <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3164,10 +3164,10 @@
         <v>1.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
@@ -3266,7 +3266,7 @@
         <v>4.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
         <v>9.199999999999999</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3406,10 +3406,10 @@
         <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>5.3</v>
@@ -3439,10 +3439,10 @@
         <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
         <v>1.12</v>
@@ -3559,7 +3559,7 @@
         <v>13.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI12" t="n">
         <v>3.25</v>
@@ -3568,49 +3568,49 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN12" t="n">
         <v>4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP12" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT12" t="n">
         <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
         <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
         <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3696,19 +3696,19 @@
         <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
         <v>27</v>
@@ -3723,7 +3723,7 @@
         <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>40</v>
@@ -3738,7 +3738,7 @@
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="n">
         <v>29</v>
@@ -3750,13 +3750,13 @@
         <v>36</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
         <v>13.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP13" t="n">
         <v>17.5</v>
@@ -3768,7 +3768,7 @@
         <v>19.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
@@ -3792,7 +3792,7 @@
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3804,7 +3804,7 @@
         <v>14.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>11</v>
@@ -3852,7 +3852,7 @@
         <v>7.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
         <v>25</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -3947,10 +3947,10 @@
         <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -3959,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
         <v>32</v>
@@ -3986,7 +3986,7 @@
         <v>9.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
@@ -4019,10 +4019,10 @@
         <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -4034,7 +4034,7 @@
         <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
         <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
         <v>5.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J15" t="n">
         <v>4.3</v>
@@ -4180,25 +4180,25 @@
         <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
         <v>1.91</v>
@@ -4207,13 +4207,13 @@
         <v>1.99</v>
       </c>
       <c r="V15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
         <v>8.800000000000001</v>
@@ -4261,7 +4261,7 @@
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AO15" t="n">
         <v>9.800000000000001</v>
@@ -4291,7 +4291,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY15" t="n">
         <v>21</v>
@@ -4300,22 +4300,22 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG15" t="n">
         <v>7.4</v>
@@ -4330,13 +4330,13 @@
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN15" t="n">
         <v>9.800000000000001</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT15" t="n">
         <v>3.8</v>
@@ -4372,7 +4372,7 @@
         <v>25</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J16" t="n">
         <v>2.84</v>
       </c>
-      <c r="H16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -4455,7 +4455,7 @@
         <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
         <v>1.98</v>
@@ -4464,13 +4464,13 @@
         <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
         <v>500</v>
@@ -4497,7 +4497,7 @@
         <v>500</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
         <v>1.8</v>
@@ -4709,7 +4709,7 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U17" t="n">
         <v>2.06</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>1.71</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
         <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
         <v>4.6</v>
@@ -4951,10 +4951,10 @@
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
         <v>1.51</v>
@@ -4966,7 +4966,7 @@
         <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>1.79</v>
@@ -5340,7 +5340,7 @@
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5435,19 +5435,19 @@
         <v>5.3</v>
       </c>
       <c r="H20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5471,10 +5471,10 @@
         <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
         <v>2.18</v>
@@ -5498,13 +5498,13 @@
         <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>42</v>
@@ -5561,31 +5561,31 @@
         <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
         <v>16</v>
       </c>
       <c r="BB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC20" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC20" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG20" t="n">
         <v>8.800000000000001</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>3.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
         <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I22" t="n">
         <v>1.97</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
         <v>5</v>
@@ -5967,10 +5967,10 @@
         <v>1.13</v>
       </c>
       <c r="P22" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R22" t="n">
         <v>1.84</v>
@@ -6009,7 +6009,7 @@
         <v>12.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>17.5</v>
@@ -6033,7 +6033,7 @@
         <v>95</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AM22" t="n">
         <v>200</v>
@@ -6042,7 +6042,7 @@
         <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP22" t="n">
         <v>18</v>
@@ -6069,7 +6069,7 @@
         <v>12.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
@@ -6081,7 +6081,7 @@
         <v>16.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
         <v>16</v>
@@ -6120,7 +6120,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BP22" t="n">
         <v>26</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
         <v>1.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S23" t="n">
         <v>1.89</v>
@@ -6236,7 +6236,7 @@
         <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V23" t="n">
         <v>2.12</v>
@@ -6254,7 +6254,7 @@
         <v>970</v>
       </c>
       <c r="AA23" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AB23" t="n">
         <v>500</v>
@@ -6269,13 +6269,13 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -6284,7 +6284,7 @@
         <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
@@ -6305,7 +6305,7 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS23" t="n">
         <v>19</v>
@@ -6335,7 +6335,7 @@
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC23" t="n">
         <v>30</v>
@@ -6347,7 +6347,7 @@
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
         <v>4.3</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G24" t="n">
         <v>12.5</v>
@@ -6517,10 +6517,10 @@
         <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AF24" t="n">
         <v>540</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.17</v>
@@ -6726,40 +6726,40 @@
         <v>1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R25" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="S25" t="n">
         <v>1.73</v>
       </c>
       <c r="T25" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="U25" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="V25" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
         <v>500</v>
       </c>
       <c r="Y25" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="Z25" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="n">
         <v>180</v>
@@ -6783,13 +6783,13 @@
         <v>500</v>
       </c>
       <c r="AH25" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI25" t="n">
         <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
         <v>500</v>
@@ -6798,16 +6798,16 @@
         <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>500</v>
       </c>
       <c r="AO25" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.8</v>
+        <v>3.05</v>
       </c>
       <c r="AQ25" t="n">
         <v>5.8</v>
@@ -6822,7 +6822,7 @@
         <v>6.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
@@ -6831,98 +6831,98 @@
         <v>5.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.9</v>
+        <v>2.92</v>
       </c>
       <c r="AY25" t="n">
         <v>5.9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA25" t="n">
         <v>5.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.6</v>
+        <v>2.86</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="BD25" t="n">
         <v>6.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BT25" t="n">
         <v>5.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="G26" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H26" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I26" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,13 +6977,13 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q26" t="n">
         <v>1.31</v>
@@ -7004,7 +7004,7 @@
         <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X26" t="n">
         <v>500</v>
@@ -7028,7 +7028,7 @@
         <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF26" t="n">
         <v>500</v>
@@ -7058,19 +7058,19 @@
         <v>10.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ26" t="n">
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT26" t="n">
         <v>13</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
         <v>11.5</v>
@@ -7106,13 +7106,13 @@
         <v>11.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
         <v>6.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="n">
         <v>8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7210,28 +7210,28 @@
         <v>1.63</v>
       </c>
       <c r="G27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H27" t="n">
         <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.19</v>
@@ -7246,7 +7246,7 @@
         <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
         <v>1.64</v>
@@ -7369,10 +7369,10 @@
         <v>32</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.6</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
@@ -7402,7 +7402,7 @@
         <v>21</v>
       </c>
       <c r="BS27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BT27" t="n">
         <v>9.199999999999999</v>
@@ -7420,17 +7420,17 @@
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BZ27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA27" t="n">
         <v>10</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>
@@ -7461,230 +7461,230 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.24</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.31</v>
-      </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>270</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>590</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>410</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>410</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
         <v>5.8</v>
       </c>
-      <c r="K28" t="n">
+      <c r="AQ28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR28" t="n">
         <v>7.2</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 18:12:48</t>
+          <t>2026-07-02 20:27:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -860,10 +860,10 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
         <v>2.88</v>
@@ -875,13 +875,13 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
@@ -890,7 +890,7 @@
         <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.71</v>
@@ -917,16 +917,16 @@
         <v>19.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>90</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
@@ -935,7 +935,7 @@
         <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -950,10 +950,10 @@
         <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
@@ -971,10 +971,10 @@
         <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AT2" t="n">
         <v>15.5</v>
@@ -986,10 +986,10 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -1001,16 +1001,16 @@
         <v>23</v>
       </c>
       <c r="BB2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD2" t="n">
         <v>23</v>
       </c>
-      <c r="BC2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G3" t="n">
         <v>1.8</v>
@@ -1237,7 +1237,7 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AW3" t="n">
         <v>7.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1398,13 +1398,13 @@
         <v>2.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
         <v>1.61</v>
@@ -1473,19 +1473,19 @@
         <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
         <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AU4" t="n">
         <v>4.8</v>
@@ -1497,31 +1497,31 @@
         <v>5.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BA4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BG4" t="n">
         <v>3.55</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
         <v>26</v>
@@ -1634,7 +1634,7 @@
         <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>1.17</v>
@@ -1733,7 +1733,7 @@
         <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
@@ -1775,7 +1775,7 @@
         <v>2.04</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BG5" t="n">
         <v>8.4</v>
@@ -1784,7 +1784,7 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>4.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP5" t="n">
         <v>6.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -1921,7 +1921,7 @@
         <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>4.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
         <v>2.78</v>
@@ -2393,7 +2393,7 @@
         <v>2.54</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
@@ -2429,52 +2429,52 @@
         <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
         <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
         <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2483,64 +2483,64 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
         <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="n">
         <v>4.6</v>
@@ -2564,7 +2564,7 @@
         <v>6.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BP8" t="n">
         <v>18.5</v>
@@ -2582,7 +2582,7 @@
         <v>6</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV8" t="n">
         <v>16.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.71</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2916,10 +2916,10 @@
         <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
         <v>1.67</v>
@@ -2928,25 +2928,25 @@
         <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z10" t="n">
         <v>95</v>
@@ -2958,31 +2958,31 @@
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>34</v>
@@ -2991,10 +2991,10 @@
         <v>310</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
         <v>18.5</v>
@@ -3006,61 +3006,61 @@
         <v>36</v>
       </c>
       <c r="AS10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
         <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
         <v>34</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH10" t="n">
         <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,7 +3069,7 @@
         <v>14.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
         <v>4.1</v>
@@ -3087,32 +3087,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY10" t="n">
         <v>12</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         <v>4.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV11" t="n">
         <v>9.199999999999999</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
         <v>5.4</v>
@@ -3568,7 +3568,7 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,13 +3580,13 @@
         <v>4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP12" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3598,7 +3598,7 @@
         <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
         <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
         <v>2.02</v>
@@ -4088,7 +4088,7 @@
         <v>4.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
         <v>9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -4183,7 +4183,7 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
@@ -4330,7 +4330,7 @@
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>2.54</v>
       </c>
       <c r="G16" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H16" t="n">
         <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J16" t="n">
         <v>2.84</v>
@@ -4596,7 +4596,7 @@
         <v>5.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4620,7 +4620,7 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -4709,7 +4709,7 @@
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
         <v>2.06</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
@@ -5376,7 +5376,7 @@
         <v>4.7</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV19" t="n">
         <v>12.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>5.3</v>
       </c>
       <c r="H20" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="I20" t="n">
         <v>1.84</v>
@@ -5447,7 +5447,7 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5600,7 +5600,7 @@
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,7 +5612,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP20" t="n">
         <v>42</v>
@@ -5630,13 +5630,13 @@
         <v>4.7</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BV20" t="n">
         <v>12.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>26</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G21" t="n">
         <v>2.76</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I21" t="n">
         <v>2.8</v>
@@ -5722,7 +5722,7 @@
         <v>1.68</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T21" t="n">
         <v>1.47</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H22" t="n">
         <v>1.82</v>
@@ -5988,7 +5988,7 @@
         <v>2.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
         <v>40</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I23" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J23" t="n">
         <v>4.7</v>
@@ -6221,7 +6221,7 @@
         <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
         <v>1.35</v>
@@ -6236,7 +6236,7 @@
         <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V23" t="n">
         <v>2.12</v>
@@ -6269,7 +6269,7 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AG23" t="n">
         <v>32</v>
@@ -6341,7 +6341,7 @@
         <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
         <v>40</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="G24" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K24" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
         <v>1.21</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1.13</v>
@@ -6478,22 +6478,22 @@
         <v>3.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S24" t="n">
         <v>1.98</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
         <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="W24" t="n">
         <v>1.1</v>
@@ -6550,13 +6550,13 @@
         <v>120</v>
       </c>
       <c r="AO24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR24" t="n">
         <v>8.4</v>
@@ -6568,43 +6568,43 @@
         <v>26</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW24" t="n">
         <v>7.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>6.8</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB24" t="n">
         <v>4.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
         <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BH24" t="n">
         <v>5.6</v>
@@ -6616,7 +6616,7 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6628,19 +6628,19 @@
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT24" t="n">
         <v>4.5</v>
@@ -6664,11 +6664,11 @@
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="I25" t="n">
         <v>1.71</v>
@@ -6714,7 +6714,7 @@
         <v>4.8</v>
       </c>
       <c r="K25" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.17</v>
@@ -6729,28 +6729,28 @@
         <v>1.09</v>
       </c>
       <c r="P25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S25" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="T25" t="n">
         <v>1.41</v>
       </c>
       <c r="U25" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V25" t="n">
         <v>2.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>500</v>
@@ -6804,58 +6804,58 @@
         <v>500</v>
       </c>
       <c r="AO25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BC25" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG25" t="n">
         <v>3</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="H26" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,7 +6977,7 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>1.1</v>
@@ -6989,16 +6989,16 @@
         <v>1.31</v>
       </c>
       <c r="R26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S26" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T26" t="n">
         <v>1.35</v>
       </c>
       <c r="U26" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="V26" t="n">
         <v>1.46</v>
@@ -7007,112 +7007,112 @@
         <v>1.55</v>
       </c>
       <c r="X26" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="Y26" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="Z26" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AB26" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AC26" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="n">
         <v>22</v>
       </c>
-      <c r="AE26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AS26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW26" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN26" t="n">
+      <c r="AX26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>10</v>
-      </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="BC26" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BD26" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="n">
         <v>8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G27" t="n">
         <v>1.75</v>
@@ -7216,13 +7216,13 @@
         <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>1.28</v>
@@ -7231,7 +7231,7 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O27" t="n">
         <v>1.19</v>
@@ -7255,7 +7255,7 @@
         <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
         <v>2.32</v>
@@ -7369,13 +7369,13 @@
         <v>32</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK27" t="n">
         <v>6.8</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
@@ -7402,7 +7402,7 @@
         <v>21</v>
       </c>
       <c r="BS27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BT27" t="n">
         <v>9.199999999999999</v>
@@ -7420,17 +7420,17 @@
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BZ27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA27" t="n">
         <v>10</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G28" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="H28" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.25</v>
@@ -7485,142 +7485,142 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="X28" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Y28" t="n">
         <v>60</v>
       </c>
       <c r="Z28" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AE28" t="n">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="AF28" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AI28" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AK28" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="n">
         <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="AN28" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR28" t="n">
         <v>5.8</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AS28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD28" t="n">
         <v>32</v>
       </c>
-      <c r="AR28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE28" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH28" t="n">
         <v>4.4</v>
@@ -7650,10 +7650,10 @@
         <v>6.8</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BR28" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
         <v>2.88</v>
@@ -887,13 +887,13 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
         <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S2" t="n">
         <v>2.32</v>
@@ -902,7 +902,7 @@
         <v>1.48</v>
       </c>
       <c r="U2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V2" t="n">
         <v>1.53</v>
@@ -914,10 +914,10 @@
         <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
         <v>90</v>
@@ -932,7 +932,7 @@
         <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
         <v>22</v>
@@ -965,10 +965,10 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
@@ -986,7 +986,7 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
         <v>17.5</v>
@@ -1004,19 +1004,19 @@
         <v>25</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1058,7 +1058,7 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
         <v>18.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
         <v>1.86</v>
@@ -1150,19 +1150,19 @@
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
         <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X3" t="n">
         <v>20</v>
@@ -1174,37 +1174,37 @@
         <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
         <v>700</v>
       </c>
       <c r="AF3" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AI3" t="n">
         <v>700</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
         <v>120</v>
@@ -1222,13 +1222,13 @@
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1237,104 +1237,104 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
         <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>1.58</v>
@@ -1395,22 +1395,22 @@
         <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
         <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
         <v>2.4</v>
@@ -1473,58 +1473,58 @@
         <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AV4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AX4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.94</v>
+        <v>2.64</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.97</v>
+        <v>2.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>1.19</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
@@ -1658,13 +1658,13 @@
         <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T5" t="n">
         <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
@@ -1673,7 +1673,7 @@
         <v>5.7</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y5" t="n">
         <v>85</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD5" t="n">
         <v>85</v>
@@ -1712,7 +1712,7 @@
         <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
         <v>50</v>
@@ -1727,10 +1727,10 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
         <v>8.800000000000001</v>
@@ -1739,13 +1739,13 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1757,28 +1757,28 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>6.2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -1894,7 +1894,7 @@
         <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>3.6</v>
@@ -1909,22 +1909,22 @@
         <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1993,7 +1993,7 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
         <v>5.6</v>
@@ -2011,10 +2011,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
@@ -2026,13 +2026,13 @@
         <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="BF6" t="n">
         <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.16</v>
@@ -2151,49 +2151,49 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1.11</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U7" t="n">
         <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X7" t="n">
         <v>500</v>
       </c>
       <c r="Y7" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z7" t="n">
         <v>500</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>350</v>
       </c>
       <c r="AA7" t="n">
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
         <v>13.5</v>
@@ -2202,7 +2202,7 @@
         <v>42</v>
       </c>
       <c r="AE7" t="n">
-        <v>700</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
         <v>17</v>
@@ -2214,52 +2214,52 @@
         <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AO7" t="n">
         <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
         <v>16</v>
       </c>
       <c r="AU7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX7" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
@@ -2268,7 +2268,7 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -2280,13 +2280,13 @@
         <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="n">
         <v>6.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -2399,46 +2399,46 @@
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V8" t="n">
         <v>1.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
         <v>22</v>
@@ -2453,7 +2453,7 @@
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE8" t="n">
         <v>26</v>
@@ -2462,7 +2462,7 @@
         <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>16</v>
@@ -2471,7 +2471,7 @@
         <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
@@ -2501,13 +2501,13 @@
         <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
         <v>20</v>
@@ -2522,7 +2522,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB8" t="n">
         <v>36</v>
@@ -2534,49 +2534,49 @@
         <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF8" t="n">
         <v>13.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
         <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT8" t="n">
         <v>6</v>
@@ -2588,13 +2588,13 @@
         <v>16.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
         <v>3.1</v>
@@ -2671,7 +2671,7 @@
         <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S9" t="n">
         <v>1.91</v>
@@ -2719,7 +2719,7 @@
         <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI9" t="n">
         <v>23</v>
@@ -2779,13 +2779,13 @@
         <v>19.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC9" t="n">
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -2889,37 +2889,37 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
         <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
         <v>1.67</v>
@@ -2928,7 +2928,7 @@
         <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
@@ -2937,16 +2937,16 @@
         <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
         <v>95</v>
@@ -2961,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>120</v>
@@ -2973,10 +2973,10 @@
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
         <v>16.5</v>
@@ -2985,31 +2985,31 @@
         <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>310</v>
       </c>
       <c r="AN10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AP10" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AS10" t="n">
         <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
         <v>9</v>
@@ -3018,25 +3018,25 @@
         <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
         <v>19.5</v>
@@ -3054,19 +3054,19 @@
         <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
@@ -3075,44 +3075,44 @@
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
         <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX10" t="n">
         <v>44</v>
       </c>
       <c r="BY10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
         <v>3.35</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -3418,7 +3418,7 @@
         <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>4.9</v>
@@ -3430,7 +3430,7 @@
         <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.53</v>
@@ -3439,10 +3439,10 @@
         <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
         <v>1.12</v>
@@ -3451,7 +3451,7 @@
         <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>38</v>
@@ -3511,10 +3511,10 @@
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -3526,7 +3526,7 @@
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -3550,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF12" t="n">
         <v>5.3</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
         <v>3.45</v>
@@ -3666,7 +3666,7 @@
         <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3702,7 +3702,7 @@
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I14" t="n">
         <v>8.4</v>
@@ -3947,7 +3947,7 @@
         <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U14" t="n">
         <v>2.02</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G15" t="n">
         <v>7</v>
@@ -4336,10 +4336,10 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO15" t="n">
         <v>7.2</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT15" t="n">
         <v>3.8</v>
@@ -4366,13 +4366,13 @@
         <v>10.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
         <v>25</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>2.54</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="H16" t="n">
         <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
         <v>2.84</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>4.7</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H17" t="n">
         <v>1.73</v>
@@ -4682,7 +4682,7 @@
         <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -4691,7 +4691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -4703,7 +4703,7 @@
         <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -4718,7 +4718,7 @@
         <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
         <v>21</v>
@@ -4745,13 +4745,13 @@
         <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
         <v>70</v>
@@ -4811,19 +4811,19 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
         <v>7.8</v>
@@ -4832,22 +4832,22 @@
         <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO17" t="n">
         <v>6.6</v>
@@ -4856,31 +4856,31 @@
         <v>44</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BV17" t="n">
         <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
         <v>2.2</v>
       </c>
       <c r="X18" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Y18" t="n">
         <v>50</v>
@@ -4987,13 +4987,13 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
         <v>12.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
@@ -5008,13 +5008,13 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AJ18" t="n">
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
@@ -5023,7 +5023,7 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
@@ -5035,10 +5035,10 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -5050,7 +5050,7 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -5062,7 +5062,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB18" t="n">
         <v>9</v>
@@ -5071,10 +5071,10 @@
         <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
         <v>7.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G19" t="n">
         <v>5</v>
@@ -5184,7 +5184,7 @@
         <v>1.79</v>
       </c>
       <c r="I19" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="J19" t="n">
         <v>3.85</v>
@@ -5223,7 +5223,7 @@
         <v>2.18</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W19" t="n">
         <v>1.25</v>
@@ -5292,10 +5292,10 @@
         <v>6.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AU19" t="n">
         <v>5.1</v>
@@ -5307,7 +5307,7 @@
         <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -5322,16 +5322,16 @@
         <v>4.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE19" t="n">
         <v>4.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG19" t="n">
         <v>9</v>
@@ -5340,55 +5340,55 @@
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="BN19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO19" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>11</v>
+        <v>3.35</v>
       </c>
       <c r="BT19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G20" t="n">
         <v>5.3</v>
@@ -5438,13 +5438,13 @@
         <v>1.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.32</v>
@@ -5477,7 +5477,7 @@
         <v>2.14</v>
       </c>
       <c r="V20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W20" t="n">
         <v>1.23</v>
@@ -5513,7 +5513,7 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -5522,13 +5522,13 @@
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AN20" t="n">
         <v>80</v>
@@ -5561,7 +5561,7 @@
         <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
@@ -5573,25 +5573,25 @@
         <v>16</v>
       </c>
       <c r="BB20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
         <v>8</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI20" t="n">
         <v>3</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN20" t="n">
         <v>8.800000000000001</v>
@@ -5618,19 +5618,19 @@
         <v>42</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20" t="n">
         <v>48</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
         <v>4.7</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV20" t="n">
         <v>12.5</v>
@@ -5642,7 +5642,7 @@
         <v>26</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
         <v>1.82</v>
@@ -5949,7 +5949,7 @@
         <v>1.97</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
         <v>5</v>
@@ -5967,13 +5967,13 @@
         <v>1.13</v>
       </c>
       <c r="P22" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S22" t="n">
         <v>1.99</v>
@@ -5982,16 +5982,16 @@
         <v>1.45</v>
       </c>
       <c r="U22" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="V22" t="n">
         <v>2.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="Y22" t="n">
         <v>18</v>
@@ -6024,7 +6024,7 @@
         <v>15.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AJ22" t="n">
         <v>470</v>
@@ -6042,7 +6042,7 @@
         <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP22" t="n">
         <v>18</v>
@@ -6069,7 +6069,7 @@
         <v>12.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
@@ -6081,7 +6081,7 @@
         <v>16.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC22" t="n">
         <v>16</v>
@@ -6108,7 +6108,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6129,7 +6129,7 @@
         <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS22" t="n">
         <v>7.4</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="I23" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J23" t="n">
         <v>4.7</v>
@@ -6224,25 +6224,25 @@
         <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R23" t="n">
         <v>1.9</v>
       </c>
       <c r="S23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T23" t="n">
         <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V23" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X23" t="n">
         <v>46</v>
@@ -6269,10 +6269,10 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AG23" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AH23" t="n">
         <v>16</v>
@@ -6284,7 +6284,7 @@
         <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
@@ -6293,7 +6293,7 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AO23" t="n">
         <v>6.8</v>
@@ -6305,7 +6305,7 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS23" t="n">
         <v>19</v>
@@ -6335,19 +6335,19 @@
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC23" t="n">
         <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE23" t="n">
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
         <v>4.3</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="J24" t="n">
         <v>5.9</v>
@@ -6475,16 +6475,16 @@
         <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
         <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T24" t="n">
         <v>1.71</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G25" t="n">
         <v>5.7</v>
@@ -6744,7 +6744,7 @@
         <v>1.41</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="V25" t="n">
         <v>2.4</v>
@@ -6813,7 +6813,7 @@
         <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS25" t="n">
         <v>5.9</v>
@@ -6825,7 +6825,7 @@
         <v>5.3</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW25" t="n">
         <v>5.5</v>
@@ -6843,7 +6843,7 @@
         <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>2.82</v>
+        <v>4.8</v>
       </c>
       <c r="BC25" t="n">
         <v>4.9</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G26" t="n">
         <v>2.54</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,13 +6977,13 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
         <v>1.1</v>
       </c>
       <c r="P26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="n">
         <v>1.31</v>
@@ -6998,7 +6998,7 @@
         <v>1.35</v>
       </c>
       <c r="U26" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="V26" t="n">
         <v>1.46</v>
@@ -7013,7 +7013,7 @@
         <v>32</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA26" t="n">
         <v>110</v>
@@ -7028,13 +7028,13 @@
         <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AF26" t="n">
         <v>32</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH26" t="n">
         <v>15.5</v>
@@ -7070,16 +7070,16 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>19</v>
       </c>
       <c r="AU26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV26" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>11</v>
       </c>
       <c r="AW26" t="n">
         <v>17.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
         <v>1.25</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
         <v>4.2</v>
@@ -7503,7 +7503,7 @@
         <v>2.84</v>
       </c>
       <c r="T28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
         <v>1.62</v>
@@ -7539,7 +7539,7 @@
         <v>490</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
@@ -7575,13 +7575,13 @@
         <v>34</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU28" t="n">
         <v>12</v>
@@ -7590,7 +7590,7 @@
         <v>42</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>6.8</v>
@@ -7602,7 +7602,7 @@
         <v>29</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB28" t="n">
         <v>8.199999999999999</v>
@@ -7614,13 +7614,13 @@
         <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
         <v>4.3</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH28" t="n">
         <v>4.4</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-02 22:42:30</t>
+          <t>2026-07-03 00:58:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -881,16 +881,16 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
         <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.72</v>
@@ -905,34 +905,34 @@
         <v>2.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
         <v>22</v>
@@ -944,40 +944,40 @@
         <v>14</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AJ2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
         <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
         <v>30</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
         <v>9</v>
@@ -989,98 +989,98 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BC2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.37</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB3" t="n">
         <v>17</v>
       </c>
-      <c r="BA3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>11</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1365,55 +1365,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I4" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
@@ -1422,37 +1422,37 @@
         <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>18</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
         <v>700</v>
@@ -1470,125 +1470,125 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.35</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU4" t="n">
         <v>3.65</v>
       </c>
-      <c r="AU4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1622,61 +1622,61 @@
         <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="R5" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="S5" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="T5" t="n">
         <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="X5" t="n">
         <v>50</v>
       </c>
       <c r="Y5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Z5" t="n">
         <v>250</v>
@@ -1685,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="n">
         <v>25</v>
@@ -1694,145 +1694,145 @@
         <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>48</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL5" t="n">
         <v>50</v>
       </c>
       <c r="AM5" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN5" t="n">
         <v>3.05</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AV5" t="n">
         <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BG5" t="n">
         <v>8.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI5" t="n">
         <v>4.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -1873,94 +1873,94 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="I6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
         <v>700</v>
@@ -1975,64 +1975,64 @@
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AO6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR6" t="n">
         <v>7</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AS6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2127,220 +2127,220 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
         <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
         <v>1.11</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
         <v>1.35</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
         <v>1.81</v>
       </c>
       <c r="T7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V7" t="n">
         <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="Y7" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="n">
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>15.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>46</v>
       </c>
       <c r="AN7" t="n">
         <v>4.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AQ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS7" t="n">
         <v>29</v>
       </c>
-      <c r="AR7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV7" t="n">
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX7" t="n">
         <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2381,100 +2381,100 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
         <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.64</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.65</v>
       </c>
       <c r="W8" t="n">
         <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2483,10 +2483,10 @@
         <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -2501,10 +2501,10 @@
         <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2528,28 +2528,28 @@
         <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK8" t="n">
         <v>5.5</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2567,34 +2567,34 @@
         <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU8" t="n">
         <v>4.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>2.3</v>
@@ -2653,34 +2653,34 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
         <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
         <v>1.76</v>
@@ -2692,19 +2692,19 @@
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB9" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
@@ -2722,7 +2722,7 @@
         <v>13.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
         <v>55</v>
@@ -2734,43 +2734,43 @@
         <v>27</v>
       </c>
       <c r="AM9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AQ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR9" t="n">
         <v>19</v>
       </c>
-      <c r="AR9" t="n">
-        <v>20</v>
-      </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
         <v>27</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>12</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2806,7 +2806,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,7 +2818,7 @@
         <v>7.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
         <v>5.9</v>
@@ -2904,49 +2904,49 @@
         <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="n">
         <v>23</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>26</v>
       </c>
       <c r="Z10" t="n">
         <v>95</v>
@@ -2955,16 +2955,16 @@
         <v>690</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
@@ -2973,146 +2973,146 @@
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK10" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AS10" t="n">
         <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM10" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>16</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY10" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3143,58 +3143,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
         <v>2.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
         <v>1.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
         <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
         <v>36</v>
@@ -3203,34 +3203,34 @@
         <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
         <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
         <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
         <v>55</v>
@@ -3242,131 +3242,131 @@
         <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH11" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="BI11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BL11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BN11" t="n">
         <v>7.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="BP11" t="n">
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BX11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3397,103 +3397,103 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="G12" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.93</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="Z12" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="AA12" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE12" t="n">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
         <v>13</v>
       </c>
       <c r="AK12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
         <v>390</v>
@@ -3502,79 +3502,79 @@
         <v>7.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>11</v>
-      </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN12" t="n">
         <v>4</v>
@@ -3583,19 +3583,19 @@
         <v>3.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU12" t="n">
         <v>6.8</v>
@@ -3604,13 +3604,13 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>2.96</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
-        <v>27</v>
+        <v>540</v>
       </c>
       <c r="AA13" t="n">
-        <v>440</v>
+        <v>280</v>
       </c>
       <c r="AB13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>13</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AR13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU13" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AV13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW13" t="n">
         <v>12</v>
       </c>
-      <c r="AH13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN13" t="n">
+      <c r="AX13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AO13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="BD13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>5.6</v>
       </c>
-      <c r="BO13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6</v>
-      </c>
       <c r="BR13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA13" t="n">
         <v>7.2</v>
       </c>
-      <c r="BU13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -3896,181 +3896,181 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8</v>
+        <v>1.61</v>
       </c>
       <c r="I14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
         <v>8.4</v>
       </c>
-      <c r="J14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>32</v>
-      </c>
       <c r="Z14" t="n">
-        <v>540</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="AG14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>480</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>240</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA14" t="n">
         <v>10</v>
       </c>
-      <c r="AH14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BC14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD14" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD14" t="n">
-        <v>16</v>
-      </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
@@ -4082,53 +4082,53 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BT14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV14" t="n">
         <v>11</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="BW14" t="n">
         <v>6.4</v>
       </c>
-      <c r="BV14" t="n">
-        <v>65</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BX14" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4150,31 +4150,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="I15" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -4183,148 +4183,148 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="BC15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD15" t="n">
         <v>8.6</v>
       </c>
-      <c r="AS15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="BE15" t="n">
         <v>9</v>
       </c>
-      <c r="AV15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
@@ -4336,43 +4336,43 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV15" t="n">
         <v>12.5</v>
       </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BW15" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BX15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4413,58 +4413,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.45</v>
       </c>
-      <c r="M16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4482,16 +4482,16 @@
         <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
         <v>500</v>
@@ -4503,7 +4503,7 @@
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
         <v>500</v>
@@ -4521,76 +4521,76 @@
         <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT16" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW16" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AX16" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="n">
         <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="BN16" t="n">
         <v>5.7</v>
@@ -4608,25 +4608,25 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.22</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4667,73 +4667,73 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
         <v>9.6</v>
@@ -4742,10 +4742,10 @@
         <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AG17" t="n">
         <v>21</v>
@@ -4754,85 +4754,85 @@
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="AL17" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AO17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>16</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4844,13 +4844,13 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17" t="n">
         <v>9</v>
       </c>
       <c r="BO17" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
         <v>44</v>
@@ -4859,28 +4859,28 @@
         <v>8</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BV17" t="n">
         <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BX17" t="n">
         <v>26</v>
       </c>
       <c r="BY17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -4921,61 +4921,61 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="G18" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="T18" t="n">
         <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="X18" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="Y18" t="n">
         <v>50</v>
@@ -4987,43 +4987,43 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AK18" t="n">
         <v>65</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
@@ -5035,34 +5035,34 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV18" t="n">
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>9</v>
@@ -5071,13 +5071,13 @@
         <v>9</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
@@ -5086,46 +5086,46 @@
         <v>4.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
         <v>4.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP18" t="n">
         <v>12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW18" t="n">
         <v>8</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5175,49 +5175,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
         <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="I19" t="n">
         <v>1.88</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
         <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
         <v>2.18</v>
@@ -5226,43 +5226,43 @@
         <v>2.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG19" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>900</v>
@@ -5280,25 +5280,25 @@
         <v>500</v>
       </c>
       <c r="AO19" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AP19" t="n">
         <v>9</v>
       </c>
       <c r="AQ19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS19" t="n">
         <v>9</v>
       </c>
-      <c r="AR19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AT19" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
@@ -5307,7 +5307,7 @@
         <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -5316,79 +5316,79 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="n">
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>3.35</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU19" t="n">
         <v>4.1</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5415,234 +5415,234 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.8</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>1.85</v>
+        <v>3.65</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.83</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.23</v>
-      </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT20" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC20" t="n">
+      <c r="BU20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>26</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5683,230 +5683,230 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="S21" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="T21" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Y21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z21" t="n">
         <v>22</v>
       </c>
-      <c r="Z21" t="n">
-        <v>28</v>
-      </c>
       <c r="AA21" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AB21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF21" t="n">
         <v>22</v>
       </c>
-      <c r="AC21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI21" t="n">
         <v>30</v>
       </c>
-      <c r="AF21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
         <v>15.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX21" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>19</v>
-      </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA21" t="n">
         <v>14.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>14.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BJ21" t="n">
         <v>8.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN21" t="n">
         <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV21" t="n">
         <v>18</v>
       </c>
       <c r="BW21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA21" t="n">
         <v>6.8</v>
       </c>
-      <c r="BX21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>6.2</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -5937,124 +5937,124 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="I22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J22" t="n">
         <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P22" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R22" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="U22" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
         <v>130</v>
       </c>
       <c r="Y22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AB22" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AC22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD22" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>17.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AG22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AJ22" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
         <v>95</v>
       </c>
       <c r="AL22" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
         <v>14.5</v>
@@ -6063,25 +6063,25 @@
         <v>10.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
         <v>8</v>
       </c>
       <c r="AY22" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC22" t="n">
         <v>16</v>
@@ -6090,77 +6090,77 @@
         <v>16</v>
       </c>
       <c r="BE22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BP22" t="n">
         <v>26</v>
       </c>
       <c r="BQ22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS22" t="n">
         <v>7.2</v>
       </c>
-      <c r="BR22" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BT22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV22" t="n">
         <v>12.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6191,70 +6191,70 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="G23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="I23" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="V23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB23" t="n">
         <v>500</v>
@@ -6263,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE23" t="n">
         <v>16.5</v>
@@ -6272,7 +6272,7 @@
         <v>500</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
         <v>16</v>
@@ -6284,43 +6284,43 @@
         <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
       </c>
       <c r="AM23" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO23" t="n">
         <v>6.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AQ23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR23" t="n">
         <v>16</v>
       </c>
-      <c r="AR23" t="n">
-        <v>7</v>
-      </c>
       <c r="AS23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
         <v>10</v>
       </c>
       <c r="AW23" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>34</v>
@@ -6335,10 +6335,10 @@
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
         <v>29</v>
@@ -6347,16 +6347,16 @@
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="G24" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="H24" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="I24" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="J24" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="R24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S24" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="T24" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="V24" t="n">
-        <v>3.55</v>
+        <v>2.26</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
         <v>540</v>
       </c>
       <c r="AG24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>120</v>
       </c>
-      <c r="AH24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK24" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="AL24" t="n">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AN24" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="AO24" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>970</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ24" t="n">
+      <c r="BT24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>970</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA24" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="G25" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="I25" t="n">
         <v>1.71</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="L25" t="n">
         <v>1.17</v>
@@ -6729,28 +6729,28 @@
         <v>1.09</v>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R25" t="n">
         <v>2.06</v>
       </c>
       <c r="S25" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="T25" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U25" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="V25" t="n">
         <v>2.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X25" t="n">
         <v>500</v>
@@ -6762,7 +6762,7 @@
         <v>40</v>
       </c>
       <c r="AA25" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AB25" t="n">
         <v>500</v>
@@ -6807,58 +6807,58 @@
         <v>4.7</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB25" t="n">
         <v>6</v>
       </c>
-      <c r="AR25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY25" t="n">
+      <c r="BC25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF25" t="n">
         <v>6</v>
       </c>
-      <c r="AZ25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
@@ -6888,16 +6888,16 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="BU25" t="n">
         <v>3.3</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -6953,55 +6953,55 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I26" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="J26" t="n">
         <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.1</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R26" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S26" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="T26" t="n">
         <v>1.35</v>
       </c>
       <c r="U26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
         <v>1.55</v>
@@ -7010,10 +7010,10 @@
         <v>120</v>
       </c>
       <c r="Y26" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Z26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
         <v>110</v>
@@ -7022,28 +7022,28 @@
         <v>40</v>
       </c>
       <c r="AC26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
         <v>32</v>
       </c>
       <c r="AF26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI26" t="n">
         <v>32</v>
       </c>
-      <c r="AG26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>25</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK26" t="n">
         <v>28</v>
@@ -7055,7 +7055,7 @@
         <v>55</v>
       </c>
       <c r="AN26" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO26" t="n">
         <v>11</v>
@@ -7064,16 +7064,16 @@
         <v>27</v>
       </c>
       <c r="AQ26" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
         <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
         <v>10.5</v>
@@ -7082,13 +7082,13 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX26" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
         <v>10.5</v>
@@ -7097,16 +7097,16 @@
         <v>16</v>
       </c>
       <c r="BB26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BC26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD26" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
@@ -7115,58 +7115,58 @@
         <v>8.4</v>
       </c>
       <c r="BH26" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BI26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ26" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BN26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>2.78</v>
+        <v>5.9</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="BT26" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G27" t="n">
         <v>1.75</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="n">
         <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.28</v>
@@ -7231,73 +7231,73 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q27" t="n">
         <v>1.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U27" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
         <v>2.32</v>
       </c>
       <c r="X27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
         <v>19.5</v>
@@ -7312,10 +7312,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ27" t="n">
         <v>18</v>
@@ -7327,19 +7327,19 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU27" t="n">
         <v>8</v>
       </c>
       <c r="AV27" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY27" t="n">
         <v>7.8</v>
@@ -7351,7 +7351,7 @@
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>11.5</v>
@@ -7366,13 +7366,13 @@
         <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH27" t="n">
         <v>4.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.4</v>
@@ -7393,7 +7393,7 @@
         <v>3.6</v>
       </c>
       <c r="BP27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ27" t="n">
         <v>7.6</v>
@@ -7405,7 +7405,7 @@
         <v>14.5</v>
       </c>
       <c r="BT27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU27" t="n">
         <v>6.6</v>
@@ -7414,7 +7414,7 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
@@ -7423,14 +7423,14 @@
         <v>27</v>
       </c>
       <c r="BZ27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>
@@ -7461,82 +7461,82 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G28" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="H28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="K28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
         <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
         <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V28" t="n">
         <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y28" t="n">
         <v>60</v>
       </c>
       <c r="Z28" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AD28" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AE28" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AF28" t="n">
         <v>7.8</v>
@@ -7545,34 +7545,34 @@
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AI28" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM28" t="n">
         <v>340</v>
       </c>
       <c r="AN28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="AR28" t="n">
         <v>5.9</v>
@@ -7584,34 +7584,34 @@
         <v>6.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>42</v>
+        <v>5.6</v>
       </c>
       <c r="AW28" t="n">
         <v>6</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA28" t="n">
         <v>5.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE28" t="n">
         <v>5.9</v>
@@ -7623,13 +7623,13 @@
         <v>6</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BJ28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BK28" t="n">
         <v>1.01</v>
@@ -7641,25 +7641,25 @@
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS28" t="n">
         <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BU28" t="n">
         <v>1.01</v>
@@ -7677,14 +7677,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 00:58:32</t>
+          <t>2026-07-03 03:14:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.76</v>
       </c>
-      <c r="I2" t="n">
-        <v>2.86</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
@@ -881,22 +881,22 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.48</v>
@@ -905,22 +905,22 @@
         <v>2.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
         <v>18</v>
@@ -935,22 +935,22 @@
         <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>14</v>
       </c>
       <c r="AI2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>28</v>
@@ -959,19 +959,19 @@
         <v>55</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>30</v>
@@ -980,28 +980,28 @@
         <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -1010,13 +1010,13 @@
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
@@ -1046,13 +1046,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR2" t="n">
         <v>23</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
@@ -1061,26 +1061,26 @@
         <v>5.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.75</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.8</v>
-      </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
         <v>320</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP3" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="BH3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>11</v>
       </c>
-      <c r="BF3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>22</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1371,13 +1371,13 @@
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>5.4</v>
@@ -1389,13 +1389,13 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="Q4" t="n">
         <v>1.48</v>
@@ -1410,10 +1410,10 @@
         <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
@@ -1422,7 +1422,7 @@
         <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
         <v>16.5</v>
@@ -1431,7 +1431,7 @@
         <v>18</v>
       </c>
       <c r="AB4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
@@ -1446,7 +1446,7 @@
         <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
@@ -1470,10 +1470,10 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
@@ -1488,10 +1488,10 @@
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>10.5</v>
@@ -1503,13 +1503,13 @@
         <v>17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BC4" t="n">
         <v>40</v>
@@ -1545,7 +1545,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO4" t="n">
         <v>5</v>
@@ -1554,7 +1554,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1566,7 +1566,7 @@
         <v>4.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="K5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1661,7 +1661,7 @@
         <v>1.98</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
         <v>1.77</v>
@@ -1670,7 +1670,7 @@
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
         <v>50</v>
@@ -1679,7 +1679,7 @@
         <v>90</v>
       </c>
       <c r="Z5" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1691,64 +1691,64 @@
         <v>25</v>
       </c>
       <c r="AD5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AE5" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI5" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ5" t="n">
         <v>9.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="AP5" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AR5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
@@ -1757,10 +1757,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
         <v>8</v>
@@ -1769,34 +1769,34 @@
         <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>2.74</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="n">
         <v>5.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
         <v>14</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>12</v>
       </c>
       <c r="BN5" t="n">
         <v>4</v>
@@ -1808,31 +1808,31 @@
         <v>6.2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>6.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.57</v>
@@ -1915,19 +1915,19 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W6" t="n">
         <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
         <v>8.4</v>
@@ -1945,10 +1945,10 @@
         <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF6" t="n">
         <v>210</v>
@@ -1957,7 +1957,7 @@
         <v>32</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>100</v>
@@ -1975,28 +1975,28 @@
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
         <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>8.6</v>
@@ -2005,46 +2005,46 @@
         <v>12.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BC6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BD6" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BG6" t="n">
         <v>7</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,10 +2053,10 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2071,10 +2071,10 @@
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.21</v>
@@ -2151,13 +2151,13 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1.11</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q7" t="n">
         <v>1.35</v>
@@ -2166,55 +2166,55 @@
         <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="T7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="X7" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Y7" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Z7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA7" t="n">
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
         <v>17.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
@@ -2226,37 +2226,37 @@
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AR7" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AS7" t="n">
         <v>29</v>
       </c>
       <c r="AT7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AU7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="n">
         <v>14.5</v>
@@ -2268,10 +2268,10 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -2283,13 +2283,13 @@
         <v>36</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI7" t="n">
         <v>4.6</v>
@@ -2298,49 +2298,49 @@
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO7" t="n">
         <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" t="n">
         <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
         <v>32</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
         <v>2.56</v>
@@ -2396,61 +2396,61 @@
         <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="V8" t="n">
         <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>12</v>
@@ -2459,7 +2459,7 @@
         <v>24</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2468,10 +2468,10 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
         <v>27</v>
@@ -2492,7 +2492,7 @@
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
@@ -2501,13 +2501,13 @@
         <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>20</v>
@@ -2534,7 +2534,7 @@
         <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
         <v>15</v>
@@ -2546,7 +2546,7 @@
         <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.6</v>
@@ -2564,13 +2564,13 @@
         <v>6.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR8" t="n">
         <v>26</v>
@@ -2579,7 +2579,7 @@
         <v>9.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
         <v>4.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
@@ -2674,10 +2674,10 @@
         <v>2.04</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
@@ -2734,10 +2734,10 @@
         <v>27</v>
       </c>
       <c r="AM9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
         <v>8.199999999999999</v>
@@ -2749,13 +2749,13 @@
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
         <v>32</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
@@ -2770,7 +2770,7 @@
         <v>27</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>12</v>
@@ -2785,7 +2785,7 @@
         <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
@@ -2803,7 +2803,7 @@
         <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK9" t="n">
         <v>6.4</v>
@@ -2812,25 +2812,25 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN9" t="n">
         <v>7.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT9" t="n">
         <v>6.4</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>4.2</v>
@@ -2913,64 +2913,64 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
         <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
         <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
         <v>690</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH10" t="n">
         <v>18.5</v>
@@ -2982,28 +2982,28 @@
         <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM10" t="n">
         <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS10" t="n">
         <v>42</v>
@@ -3012,13 +3012,13 @@
         <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3036,83 +3036,83 @@
         <v>15.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
         <v>36</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
         <v>55</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
         <v>6</v>
       </c>
       <c r="BL10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
         <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BV10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX10" t="n">
         <v>44</v>
       </c>
-      <c r="BW10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>46</v>
-      </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA10" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3143,31 +3143,31 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
@@ -3176,7 +3176,7 @@
         <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
         <v>1.74</v>
@@ -3185,7 +3185,7 @@
         <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="U11" t="n">
         <v>2.74</v>
@@ -3197,10 +3197,10 @@
         <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
@@ -3218,10 +3218,10 @@
         <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG11" t="n">
         <v>15.5</v>
@@ -3236,7 +3236,7 @@
         <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -3245,13 +3245,13 @@
         <v>50</v>
       </c>
       <c r="AN11" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO11" t="n">
         <v>10.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>14.5</v>
@@ -3260,7 +3260,7 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT11" t="n">
         <v>17</v>
@@ -3278,25 +3278,25 @@
         <v>21</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD11" t="n">
         <v>20</v>
       </c>
-      <c r="BD11" t="n">
-        <v>18</v>
-      </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF11" t="n">
         <v>12</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G12" t="n">
         <v>1.49</v>
@@ -3406,13 +3406,13 @@
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -3421,28 +3421,28 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
@@ -3451,25 +3451,25 @@
         <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="Z12" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AA12" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
         <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
         <v>120</v>
@@ -3478,13 +3478,13 @@
         <v>9</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AJ12" t="n">
         <v>13</v>
@@ -3496,37 +3496,37 @@
         <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
         <v>26</v>
       </c>
       <c r="AR12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
         <v>26</v>
       </c>
       <c r="AW12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AX12" t="n">
         <v>8</v>
@@ -3538,79 +3538,79 @@
         <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.5</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO12" t="n">
         <v>3.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT12" t="n">
         <v>11.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
         <v>1.51</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.7</v>
@@ -3675,10 +3675,10 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
         <v>2.32</v>
@@ -3687,16 +3687,16 @@
         <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
         <v>2.84</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
         <v>1.14</v>
@@ -3708,16 +3708,16 @@
         <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z13" t="n">
         <v>540</v>
       </c>
       <c r="AA13" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC13" t="n">
         <v>11</v>
@@ -3738,7 +3738,7 @@
         <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="n">
         <v>13.5</v>
@@ -3753,7 +3753,7 @@
         <v>390</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO13" t="n">
         <v>150</v>
@@ -3762,13 +3762,13 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>13</v>
       </c>
-      <c r="AR13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AS13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT13" t="n">
         <v>8.4</v>
@@ -3777,22 +3777,22 @@
         <v>9.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BB13" t="n">
         <v>11.5</v>
@@ -3801,16 +3801,16 @@
         <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="n">
         <v>4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -3908,19 +3908,19 @@
         <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
@@ -3929,7 +3929,7 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
@@ -3938,28 +3938,28 @@
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
         <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
         <v>8.4</v>
@@ -3968,19 +3968,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB14" t="n">
         <v>21</v>
       </c>
       <c r="AC14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD14" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD14" t="n">
-        <v>10</v>
-      </c>
       <c r="AE14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF14" t="n">
         <v>55</v>
@@ -3989,136 +3989,136 @@
         <v>24</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AK14" t="n">
         <v>480</v>
       </c>
       <c r="AL14" t="n">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="AM14" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AO14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP14" t="n">
         <v>14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AS14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AV14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
         <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BB14" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>3.55</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BN14" t="n">
         <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BV14" t="n">
         <v>11</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -4183,34 +4183,34 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
         <v>18</v>
@@ -4222,13 +4222,13 @@
         <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="n">
         <v>19.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>10.5</v>
@@ -4243,7 +4243,7 @@
         <v>21</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>34</v>
@@ -4270,31 +4270,31 @@
         <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AS15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT15" t="n">
         <v>16.5</v>
       </c>
-      <c r="AT15" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX15" t="n">
         <v>32</v>
       </c>
       <c r="AY15" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>16</v>
@@ -4303,22 +4303,22 @@
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="n">
         <v>3.8</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
@@ -4443,28 +4443,28 @@
         <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>2.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
         <v>1.99</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4515,10 +4515,10 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
         <v>5.8</v>
@@ -4530,46 +4530,46 @@
         <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
         <v>5.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
         <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
         <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
         <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
         <v>6.8</v>
@@ -4578,13 +4578,13 @@
         <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,7 +4596,7 @@
         <v>5.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4614,19 +4614,19 @@
         <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -4706,16 +4706,16 @@
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W17" t="n">
         <v>1.22</v>
@@ -4739,13 +4739,13 @@
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG17" t="n">
         <v>21</v>
@@ -4760,19 +4760,19 @@
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AL17" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="AN17" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
@@ -4799,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AY17" t="n">
         <v>17</v>
@@ -4808,22 +4808,22 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BG17" t="n">
         <v>8.6</v>
@@ -4838,31 +4838,31 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN17" t="n">
         <v>9</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP17" t="n">
         <v>44</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR17" t="n">
         <v>50</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT17" t="n">
         <v>4.6</v>
@@ -4871,16 +4871,16 @@
         <v>3.45</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>26</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -4957,31 +4957,31 @@
         <v>1.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
         <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y18" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="Z18" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
@@ -4990,97 +4990,97 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AE18" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AJ18" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>65</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
         <v>500</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
       </c>
       <c r="AN18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO18" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BF18" t="n">
         <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BH18" t="n">
         <v>4.3</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>4.9</v>
@@ -5107,16 +5107,16 @@
         <v>4.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT18" t="n">
         <v>8.6</v>
@@ -5125,16 +5125,16 @@
         <v>5.3</v>
       </c>
       <c r="BV18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.35</v>
@@ -5208,7 +5208,7 @@
         <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R19" t="n">
         <v>1.45</v>
@@ -5217,16 +5217,16 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5244,7 +5244,7 @@
         <v>500</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
@@ -5277,7 +5277,7 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
         <v>29</v>
@@ -5286,7 +5286,7 @@
         <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
         <v>10.5</v>
@@ -5298,7 +5298,7 @@
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
@@ -5307,7 +5307,7 @@
         <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -5316,19 +5316,19 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB19" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB19" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BC19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
         <v>9.199999999999999</v>
@@ -5340,22 +5340,22 @@
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO19" t="n">
         <v>6</v>
@@ -5364,31 +5364,31 @@
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT19" t="n">
         <v>4.7</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BV19" t="n">
         <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5429,76 +5429,76 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.32</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.4</v>
       </c>
       <c r="V20" t="n">
         <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
         <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
         <v>15.5</v>
@@ -5507,7 +5507,7 @@
         <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -5516,40 +5516,40 @@
         <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
         <v>22</v>
       </c>
       <c r="AL20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO20" t="n">
         <v>38</v>
       </c>
-      <c r="AM20" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN20" t="n">
+      <c r="AP20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>13</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
@@ -5558,7 +5558,7 @@
         <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
@@ -5567,16 +5567,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
         <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
         <v>26</v>
@@ -5585,13 +5585,13 @@
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BI20" t="n">
         <v>3.25</v>
@@ -5600,34 +5600,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT20" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>7.4</v>
       </c>
       <c r="BU20" t="n">
         <v>5.5</v>
@@ -5636,13 +5636,13 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I21" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
@@ -5707,52 +5707,52 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R21" t="n">
         <v>1.63</v>
       </c>
       <c r="S21" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AB21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
         <v>13</v>
@@ -5770,22 +5770,22 @@
         <v>15.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
         <v>40</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO21" t="n">
         <v>14.5</v>
@@ -5794,31 +5794,31 @@
         <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>8.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
         <v>12.5</v>
@@ -5827,7 +5827,7 @@
         <v>14.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
@@ -5836,19 +5836,19 @@
         <v>14.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="n">
         <v>4.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21" t="n">
         <v>8.6</v>
@@ -5860,34 +5860,34 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN21" t="n">
         <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW21" t="n">
         <v>7</v>
@@ -5896,17 +5896,17 @@
         <v>25</v>
       </c>
       <c r="BY21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -5937,230 +5937,230 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
         <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="I22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U22" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V22" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="W22" t="n">
         <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Z22" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AB22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE22" t="n">
         <v>17.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AG22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AK22" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT22" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AU22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AV22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
         <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AY22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BD22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BJ22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK22" t="n">
         <v>4.6</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BM22" t="n">
         <v>8.4</v>
       </c>
       <c r="BN22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS22" t="n">
         <v>7</v>
       </c>
-      <c r="BR22" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BT22" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV22" t="n">
         <v>12.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I23" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6215,64 +6215,64 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U23" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V23" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
       </c>
       <c r="Y23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
         <v>18.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AB23" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AC23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AH23" t="n">
         <v>16</v>
@@ -6284,19 +6284,19 @@
         <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AL23" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP23" t="n">
         <v>32</v>
@@ -6314,7 +6314,7 @@
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV23" t="n">
         <v>10</v>
@@ -6323,7 +6323,7 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AY23" t="n">
         <v>15.5</v>
@@ -6335,10 +6335,10 @@
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BD23" t="n">
         <v>29</v>
@@ -6347,16 +6347,16 @@
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6445,28 +6445,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="G24" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="I24" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
         <v>6.8</v>
@@ -6475,200 +6475,200 @@
         <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S24" t="n">
         <v>2.16</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="V24" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="AC24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
         <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>540</v>
+        <v>65</v>
       </c>
       <c r="AG24" t="n">
         <v>23</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AJ24" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AK24" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
-        <v>240</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AN24" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AO24" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AP24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS24" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS24" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AT24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AX24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="BC24" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BE24" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF24" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BG24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH24" t="n">
         <v>5.4</v>
       </c>
-      <c r="BH24" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BI24" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BN24" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="BO24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BT24" t="n">
         <v>5.1</v>
       </c>
-      <c r="BP24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>5</v>
-      </c>
       <c r="BU24" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BV24" t="n">
         <v>10.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6699,172 +6699,172 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G25" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="I25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="S25" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="U25" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="V25" t="n">
         <v>2.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>500</v>
       </c>
       <c r="Y25" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="Z25" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AB25" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AC25" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD25" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
         <v>500</v>
       </c>
       <c r="AG25" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AH25" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AJ25" t="n">
         <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AL25" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM25" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN25" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AO25" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH25" t="n">
         <v>7</v>
       </c>
-      <c r="AW25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI25" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
@@ -6888,19 +6888,19 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.69</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.68</v>
+        <v>6.4</v>
       </c>
       <c r="BT25" t="n">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
@@ -6918,11 +6918,11 @@
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -6977,31 +6977,31 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.1</v>
       </c>
       <c r="P26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R26" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T26" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
         <v>1.55</v>
@@ -7010,16 +7010,16 @@
         <v>120</v>
       </c>
       <c r="Y26" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
         <v>110</v>
       </c>
       <c r="AB26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AC26" t="n">
         <v>14</v>
@@ -7028,16 +7028,16 @@
         <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="n">
         <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>32</v>
@@ -7046,7 +7046,7 @@
         <v>90</v>
       </c>
       <c r="AK26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
         <v>30</v>
@@ -7055,7 +7055,7 @@
         <v>55</v>
       </c>
       <c r="AN26" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO26" t="n">
         <v>11</v>
@@ -7070,7 +7070,7 @@
         <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AT26" t="n">
         <v>18</v>
@@ -7082,25 +7082,25 @@
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
         <v>10.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD26" t="n">
         <v>15.5</v>
@@ -7130,7 +7130,7 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN26" t="n">
         <v>7</v>
@@ -7142,7 +7142,7 @@
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
@@ -7154,13 +7154,13 @@
         <v>7.4</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7210,13 +7210,13 @@
         <v>1.65</v>
       </c>
       <c r="G27" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
       </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="n">
         <v>4.3</v>
@@ -7234,7 +7234,7 @@
         <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P27" t="n">
         <v>2.58</v>
@@ -7249,22 +7249,22 @@
         <v>2.42</v>
       </c>
       <c r="T27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U27" t="n">
         <v>2.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -7273,10 +7273,10 @@
         <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
         <v>25</v>
@@ -7285,10 +7285,10 @@
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
         <v>21</v>
@@ -7297,7 +7297,7 @@
         <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
         <v>19.5</v>
@@ -7369,7 +7369,7 @@
         <v>30</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI27" t="n">
         <v>3.5</v>
@@ -7384,10 +7384,10 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BN27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO27" t="n">
         <v>3.6</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
         <v>19.5</v>
       </c>
       <c r="J28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
         <v>1.33</v>
@@ -7488,7 +7488,7 @@
         <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
@@ -7503,7 +7503,7 @@
         <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U28" t="n">
         <v>1.64</v>
@@ -7515,37 +7515,37 @@
         <v>4.7</v>
       </c>
       <c r="X28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
         <v>60</v>
       </c>
       <c r="Z28" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD28" t="n">
         <v>90</v>
       </c>
       <c r="AE28" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AF28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AI28" t="n">
         <v>330</v>
@@ -7572,13 +7572,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT28" t="n">
         <v>6.4</v>
@@ -7587,10 +7587,10 @@
         <v>12.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX28" t="n">
         <v>6.2</v>
@@ -7602,10 +7602,10 @@
         <v>30</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
         <v>13.5</v>
@@ -7614,13 +7614,13 @@
         <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BH28" t="n">
         <v>4.3</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 03:14:28</t>
+          <t>2026-07-03 05:30:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -860,227 +860,227 @@
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="U2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD2" t="n">
         <v>24</v>
       </c>
-      <c r="BB2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>23</v>
-      </c>
       <c r="BE2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP2" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1111,67 +1111,67 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1180,161 +1180,161 @@
         <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>230</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB3" t="n">
         <v>18.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="BC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN3" t="n">
         <v>4.8</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW3" t="n">
         <v>7.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
         <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1365,55 +1365,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="I4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q4" t="n">
         <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
@@ -1428,19 +1428,19 @@
         <v>16.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF4" t="n">
         <v>500</v>
@@ -1470,10 +1470,10 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
@@ -1482,16 +1482,16 @@
         <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
         <v>10.5</v>
@@ -1500,7 +1500,7 @@
         <v>40</v>
       </c>
       <c r="AY4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>14</v>
@@ -1512,25 +1512,25 @@
         <v>40</v>
       </c>
       <c r="BC4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
         <v>46</v>
       </c>
       <c r="BF4" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,10 +1542,10 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
         <v>5</v>
@@ -1554,7 +1554,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1563,16 +1563,16 @@
         <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
         <v>1.19</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>1.22</v>
@@ -1646,10 +1646,10 @@
         <v>7.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q5" t="n">
         <v>1.39</v>
@@ -1661,22 +1661,22 @@
         <v>1.98</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="X5" t="n">
         <v>50</v>
       </c>
       <c r="Y5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="n">
         <v>230</v>
@@ -1685,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
         <v>25</v>
@@ -1697,10 +1697,10 @@
         <v>340</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>46</v>
@@ -1709,7 +1709,7 @@
         <v>230</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AK5" t="n">
         <v>17</v>
@@ -1718,7 +1718,7 @@
         <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AN5" t="n">
         <v>3</v>
@@ -1727,7 +1727,7 @@
         <v>380</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.4</v>
@@ -1736,49 +1736,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5" t="n">
         <v>7.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
         <v>12</v>
       </c>
       <c r="BD5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>2.74</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="n">
         <v>5.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -1873,79 +1873,79 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
         <v>2.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA6" t="n">
         <v>18.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1957,7 +1957,7 @@
         <v>32</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>100</v>
@@ -1975,76 +1975,76 @@
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AO6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
         <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BC6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BD6" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="BF6" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,10 +2053,10 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2071,10 +2071,10 @@
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.58</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="H7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>5.5</v>
       </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="R7" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="S7" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="T7" t="n">
         <v>1.43</v>
@@ -2175,103 +2175,103 @@
         <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="X7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Z7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA7" t="n">
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AO7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AQ7" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AR7" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AS7" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW7" t="n">
         <v>42</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -2283,64 +2283,64 @@
         <v>36</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BG7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>10</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BR7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2384,145 +2384,145 @@
         <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
         <v>2.56</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.62</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
         <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
         <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
         <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
         <v>20</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
         <v>36</v>
@@ -2531,7 +2531,7 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
@@ -2540,25 +2540,25 @@
         <v>15</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN8" t="n">
         <v>6.4</v>
@@ -2570,16 +2570,16 @@
         <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR8" t="n">
         <v>26</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU8" t="n">
         <v>4.7</v>
@@ -2588,13 +2588,13 @@
         <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
         <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
@@ -2644,7 +2644,7 @@
         <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
@@ -2659,46 +2659,46 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="T9" t="n">
         <v>1.38</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
         <v>28</v>
@@ -2722,7 +2722,7 @@
         <v>13.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ9" t="n">
         <v>55</v>
@@ -2731,7 +2731,7 @@
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>48</v>
@@ -2740,16 +2740,16 @@
         <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
         <v>32</v>
@@ -2764,7 +2764,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>27</v>
@@ -2791,7 +2791,7 @@
         <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
         <v>7.2</v>
@@ -2800,10 +2800,10 @@
         <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BK9" t="n">
         <v>6.4</v>
@@ -2812,10 +2812,10 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO9" t="n">
         <v>4.9</v>
@@ -2824,13 +2824,13 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
         <v>6.4</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.34</v>
@@ -2913,25 +2913,25 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
         <v>2.28</v>
@@ -2940,16 +2940,16 @@
         <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
         <v>690</v>
@@ -2958,16 +2958,16 @@
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>9.6</v>
@@ -2976,13 +2976,13 @@
         <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
@@ -2991,22 +2991,22 @@
         <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
         <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS10" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -3015,10 +3015,10 @@
         <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3033,49 +3033,49 @@
         <v>55</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
         <v>55</v>
       </c>
       <c r="BH10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO10" t="n">
         <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.6</v>
@@ -3084,35 +3084,35 @@
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.24</v>
@@ -3167,64 +3167,64 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
         <v>1.44</v>
       </c>
       <c r="U11" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB11" t="n">
         <v>22</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>24</v>
       </c>
       <c r="AC11" t="n">
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
         <v>15.5</v>
@@ -3233,49 +3233,49 @@
         <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT11" t="n">
         <v>17</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
@@ -3284,25 +3284,25 @@
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
         <v>36</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>5.3</v>
@@ -3314,59 +3314,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>65</v>
       </c>
       <c r="BM11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX11" t="n">
         <v>22</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11" t="n">
         <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3400,31 +3400,31 @@
         <v>1.46</v>
       </c>
       <c r="G12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
         <v>2.28</v>
@@ -3433,46 +3433,46 @@
         <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
         <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="Z12" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AB12" t="n">
         <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AE12" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF12" t="n">
         <v>9</v>
@@ -3487,7 +3487,7 @@
         <v>260</v>
       </c>
       <c r="AJ12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK12" t="n">
         <v>15</v>
@@ -3499,7 +3499,7 @@
         <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO12" t="n">
         <v>140</v>
@@ -3511,10 +3511,10 @@
         <v>26</v>
       </c>
       <c r="AR12" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AS12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
@@ -3526,7 +3526,7 @@
         <v>26</v>
       </c>
       <c r="AW12" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AX12" t="n">
         <v>8</v>
@@ -3550,67 +3550,67 @@
         <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
         <v>6</v>
       </c>
       <c r="BG12" t="n">
-        <v>16.5</v>
+        <v>80</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN12" t="n">
         <v>3.95</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
         <v>1.51</v>
@@ -3660,10 +3660,10 @@
         <v>7.4</v>
       </c>
       <c r="I13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -3681,16 +3681,16 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T13" t="n">
         <v>1.9</v>
@@ -3705,16 +3705,16 @@
         <v>2.96</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="n">
         <v>28</v>
       </c>
       <c r="Z13" t="n">
-        <v>540</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB13" t="n">
         <v>9.4</v>
@@ -3723,31 +3723,31 @@
         <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG13" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
         <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
         <v>13.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
         <v>390</v>
@@ -3759,58 +3759,58 @@
         <v>150</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BF13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="n">
         <v>4</v>
@@ -3852,7 +3852,7 @@
         <v>11.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV13" t="n">
         <v>65</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -3920,10 +3920,10 @@
         <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3932,7 +3932,7 @@
         <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
         <v>2.04</v>
@@ -3947,10 +3947,10 @@
         <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
         <v>2.52</v>
@@ -3998,7 +3998,7 @@
         <v>180</v>
       </c>
       <c r="AK14" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="AL14" t="n">
         <v>90</v>
@@ -4037,7 +4037,7 @@
         <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -4058,49 +4058,49 @@
         <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BF14" t="n">
         <v>19</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BN14" t="n">
         <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>14</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>14.5</v>
       </c>
       <c r="BT14" t="n">
         <v>4.1</v>
@@ -4109,16 +4109,16 @@
         <v>3.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
         <v>26</v>
       </c>
       <c r="BY14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -4159,43 +4159,43 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G15" t="n">
         <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="I15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
         <v>3.15</v>
@@ -4207,13 +4207,13 @@
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W15" t="n">
         <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
         <v>10</v>
@@ -4228,13 +4228,13 @@
         <v>19.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>10.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="n">
         <v>42</v>
@@ -4243,7 +4243,7 @@
         <v>21</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
         <v>34</v>
@@ -4252,25 +4252,25 @@
         <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15" t="n">
         <v>9.800000000000001</v>
@@ -4303,31 +4303,31 @@
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>46</v>
       </c>
       <c r="BE15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BG15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK15" t="n">
         <v>7.6</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15" t="n">
         <v>8.800000000000001</v>
@@ -4348,19 +4348,19 @@
         <v>42</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR15" t="n">
         <v>48</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>4.7</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV15" t="n">
         <v>12.5</v>
@@ -4372,7 +4372,7 @@
         <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.47</v>
@@ -4437,34 +4437,34 @@
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
         <v>2.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4479,7 +4479,7 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
@@ -4494,10 +4494,10 @@
         <v>970</v>
       </c>
       <c r="AG16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH16" t="n">
         <v>500</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>970</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -4524,52 +4524,52 @@
         <v>5.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU16" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6</v>
-      </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
         <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF16" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7</v>
       </c>
       <c r="BG16" t="n">
         <v>6.8</v>
@@ -4578,13 +4578,13 @@
         <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4593,40 +4593,40 @@
         <v>8.4</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4670,13 @@
         <v>5.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.85</v>
@@ -4685,49 +4685,49 @@
         <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.28</v>
       </c>
       <c r="P17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA17" t="n">
         <v>19.5</v>
@@ -4745,10 +4745,10 @@
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>20</v>
@@ -4766,22 +4766,22 @@
         <v>95</v>
       </c>
       <c r="AM17" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>8</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS17" t="n">
         <v>15.5</v>
@@ -4799,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY17" t="n">
         <v>17</v>
@@ -4808,37 +4808,37 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BC17" t="n">
         <v>44</v>
       </c>
       <c r="BD17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE17" t="n">
         <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4850,19 +4850,19 @@
         <v>9</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
         <v>44</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR17" t="n">
         <v>50</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
         <v>4.6</v>
@@ -4871,13 +4871,13 @@
         <v>3.45</v>
       </c>
       <c r="BV17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY17" t="n">
         <v>7.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
         <v>5.1</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
@@ -4945,22 +4945,22 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R18" t="n">
         <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
         <v>1.66</v>
@@ -4972,13 +4972,13 @@
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z18" t="n">
         <v>110</v>
@@ -4990,13 +4990,13 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AF18" t="n">
         <v>13.5</v>
@@ -5005,25 +5005,25 @@
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AJ18" t="n">
         <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
         <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO18" t="n">
         <v>600</v>
@@ -5038,13 +5038,13 @@
         <v>30</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
         <v>15.5</v>
@@ -5059,7 +5059,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
         <v>34</v>
@@ -5068,7 +5068,7 @@
         <v>14.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD18" t="n">
         <v>22</v>
@@ -5080,7 +5080,7 @@
         <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH18" t="n">
         <v>4.3</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
         <v>4.9</v>
@@ -5107,16 +5107,16 @@
         <v>4.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT18" t="n">
         <v>8.6</v>
@@ -5128,13 +5128,13 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H19" t="n">
         <v>1.87</v>
       </c>
       <c r="I19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -5217,16 +5217,16 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5283,22 +5283,22 @@
         <v>29</v>
       </c>
       <c r="AP19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR19" t="n">
         <v>10.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV19" t="n">
         <v>9</v>
@@ -5307,31 +5307,31 @@
         <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>11.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
         <v>9.199999999999999</v>
@@ -5340,25 +5340,25 @@
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN19" t="n">
         <v>8</v>
       </c>
       <c r="BO19" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5370,25 +5370,25 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT19" t="n">
         <v>4.7</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BV19" t="n">
         <v>12.5</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
         <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
         <v>3.9</v>
@@ -5450,7 +5450,7 @@
         <v>1.36</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
         <v>4.4</v>
@@ -5459,7 +5459,7 @@
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
         <v>1.84</v>
@@ -5471,145 +5471,145 @@
         <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
         <v>1.84</v>
       </c>
       <c r="X20" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
         <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
         <v>75</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM20" t="n">
         <v>90</v>
       </c>
-      <c r="AF20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>200</v>
-      </c>
       <c r="AN20" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB20" t="n">
         <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
         <v>22</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN20" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5.4</v>
       </c>
       <c r="BO20" t="n">
         <v>4.5</v>
@@ -5618,31 +5618,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT20" t="n">
         <v>7.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H21" t="n">
         <v>2.56</v>
@@ -5695,13 +5695,13 @@
         <v>2.66</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -5710,52 +5710,52 @@
         <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U21" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="V21" t="n">
         <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>48</v>
       </c>
       <c r="AB21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC21" t="n">
         <v>10</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -5773,40 +5773,40 @@
         <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK21" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
       </c>
       <c r="AS21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU21" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8.6</v>
       </c>
       <c r="AV21" t="n">
         <v>10.5</v>
@@ -5827,7 +5827,7 @@
         <v>14.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
@@ -5839,46 +5839,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BJ21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN21" t="n">
         <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT21" t="n">
         <v>6.2</v>
@@ -5887,26 +5887,26 @@
         <v>5.2</v>
       </c>
       <c r="BV21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>17.5</v>
       </c>
-      <c r="BW21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>16.5</v>
-      </c>
       <c r="CA21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -5943,70 +5943,70 @@
         <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R22" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="S22" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="T22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W22" t="n">
         <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="Y22" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
         <v>27</v>
       </c>
       <c r="AB22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
@@ -6015,16 +6015,16 @@
         <v>17.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AG22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="n">
         <v>85</v>
@@ -6033,16 +6033,16 @@
         <v>46</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
         <v>29</v>
@@ -6051,13 +6051,13 @@
         <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
         <v>18</v>
       </c>
       <c r="AT22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU22" t="n">
         <v>12</v>
@@ -6078,31 +6078,31 @@
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
       </c>
       <c r="BD22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF22" t="n">
         <v>12</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BH22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BI22" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.4</v>
@@ -6111,13 +6111,13 @@
         <v>4.6</v>
       </c>
       <c r="BL22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO22" t="n">
         <v>6.8</v>
@@ -6126,7 +6126,7 @@
         <v>24</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
         <v>23</v>
@@ -6135,32 +6135,32 @@
         <v>7</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BY22" t="n">
         <v>6.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -6191,79 +6191,79 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J23" t="n">
         <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R23" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="T23" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="U23" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V23" t="n">
         <v>2.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD23" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>16.5</v>
@@ -6275,7 +6275,7 @@
         <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -6284,22 +6284,22 @@
         <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ23" t="n">
         <v>17</v>
@@ -6314,7 +6314,7 @@
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AV23" t="n">
         <v>10</v>
@@ -6329,37 +6329,37 @@
         <v>15.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC23" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BE23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK23" t="n">
         <v>1.01</v>
@@ -6389,10 +6389,10 @@
         <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
@@ -6410,11 +6410,11 @@
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K24" t="n">
         <v>5.6</v>
@@ -6469,40 +6469,40 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
         <v>2.16</v>
       </c>
       <c r="T24" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X24" t="n">
         <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z24" t="n">
         <v>12.5</v>
@@ -6511,58 +6511,58 @@
         <v>15.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
         <v>13.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AG24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
         <v>700</v>
       </c>
       <c r="AK24" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AL24" t="n">
         <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AO24" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AP24" t="n">
         <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
         <v>25</v>
@@ -6571,7 +6571,7 @@
         <v>11</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
         <v>11</v>
@@ -6583,28 +6583,28 @@
         <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
         <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>85</v>
+        <v>10.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BE24" t="n">
         <v>60</v>
       </c>
       <c r="BF24" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH24" t="n">
         <v>5.4</v>
@@ -6622,31 +6622,31 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BN24" t="n">
         <v>11</v>
       </c>
       <c r="BO24" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV24" t="n">
         <v>10.5</v>
@@ -6658,7 +6658,7 @@
         <v>23</v>
       </c>
       <c r="BY24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>12.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H25" t="n">
         <v>1.56</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J25" t="n">
         <v>4.9</v>
@@ -6717,7 +6717,7 @@
         <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
@@ -6729,16 +6729,16 @@
         <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R25" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S25" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T25" t="n">
         <v>1.37</v>
@@ -6747,7 +6747,7 @@
         <v>3.05</v>
       </c>
       <c r="V25" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="W25" t="n">
         <v>1.22</v>
@@ -6756,10 +6756,10 @@
         <v>500</v>
       </c>
       <c r="Y25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA25" t="n">
         <v>24</v>
@@ -6768,13 +6768,13 @@
         <v>200</v>
       </c>
       <c r="AC25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AD25" t="n">
         <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="n">
         <v>500</v>
@@ -6786,16 +6786,16 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ25" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK25" t="n">
         <v>200</v>
       </c>
       <c r="AL25" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AM25" t="n">
         <v>130</v>
@@ -6807,40 +6807,40 @@
         <v>4.3</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="AQ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS25" t="n">
         <v>15</v>
       </c>
-      <c r="AR25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AT25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AU25" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX25" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AY25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ25" t="n">
         <v>11.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>50</v>
@@ -6912,7 +6912,7 @@
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -6953,16 +6953,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="I26" t="n">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="J26" t="n">
         <v>4.3</v>
@@ -6989,67 +6989,67 @@
         <v>1.32</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="T26" t="n">
         <v>1.34</v>
       </c>
       <c r="U26" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="W26" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="X26" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="Y26" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF26" t="n">
         <v>36</v>
       </c>
-      <c r="Z26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>34</v>
-      </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AM26" t="n">
         <v>55</v>
@@ -7058,73 +7058,73 @@
         <v>9.4</v>
       </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AQ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="n">
         <v>18.5</v>
       </c>
-      <c r="AR26" t="n">
-        <v>19</v>
-      </c>
       <c r="AS26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AU26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV26" t="n">
         <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BC26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH26" t="n">
         <v>6.4</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7133,34 +7133,34 @@
         <v>8</v>
       </c>
       <c r="BN26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT26" t="n">
         <v>7</v>
       </c>
-      <c r="BO26" t="n">
+      <c r="BU26" t="n">
         <v>5.1</v>
       </c>
-      <c r="BP26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ26" t="n">
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
         <v>6</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>6.2</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -7231,31 +7231,31 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P27" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R27" t="n">
         <v>1.63</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
         <v>2.34</v>
@@ -7306,7 +7306,7 @@
         <v>32</v>
       </c>
       <c r="AM27" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="n">
         <v>8.199999999999999</v>
@@ -7369,10 +7369,10 @@
         <v>30</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.4</v>
@@ -7384,13 +7384,13 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BN27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP27" t="n">
         <v>10.5</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>1.25</v>
       </c>
       <c r="G28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H28" t="n">
         <v>16</v>
@@ -7488,7 +7488,7 @@
         <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
@@ -7503,7 +7503,7 @@
         <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
         <v>1.64</v>
@@ -7512,7 +7512,7 @@
         <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X28" t="n">
         <v>24</v>
@@ -7530,7 +7530,7 @@
         <v>7.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AD28" t="n">
         <v>90</v>
@@ -7551,7 +7551,7 @@
         <v>330</v>
       </c>
       <c r="AJ28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK28" t="n">
         <v>17</v>
@@ -7563,7 +7563,7 @@
         <v>340</v>
       </c>
       <c r="AN28" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
@@ -7572,13 +7572,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
         <v>6.4</v>
@@ -7587,10 +7587,10 @@
         <v>12.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX28" t="n">
         <v>6.2</v>
@@ -7602,7 +7602,7 @@
         <v>30</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB28" t="n">
         <v>8.199999999999999</v>
@@ -7614,13 +7614,13 @@
         <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="n">
         <v>4.3</v>
@@ -7641,7 +7641,7 @@
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO28" t="n">
         <v>3.1</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 05:30:36</t>
+          <t>2026-07-03 07:47:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>5.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>7.2</v>
+        <v>2.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="U2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19</v>
+        <v>1.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>1.06</v>
       </c>
       <c r="AS2" t="n">
-        <v>36</v>
+        <v>1.06</v>
       </c>
       <c r="AT2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.4</v>
+        <v>2.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>1.06</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>1.06</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>1.06</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>2.36</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>1.06</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>1.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>1.06</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>2.36</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>1.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.6</v>
+        <v>130</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.8</v>
+        <v>130</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>130</v>
       </c>
       <c r="BR2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>12.5</v>
+        <v>1.12</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>12.5</v>
+        <v>1.12</v>
       </c>
       <c r="BZ2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>17</v>
@@ -1174,46 +1174,46 @@
         <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21</v>
-      </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
         <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
         <v>100</v>
@@ -1228,113 +1228,113 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BV3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1371,85 +1371,85 @@
         <v>5.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I4" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>38</v>
@@ -1470,40 +1470,40 @@
         <v>700</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT4" t="n">
         <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>40</v>
       </c>
       <c r="AY4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
         <v>19</v>
@@ -1512,25 +1512,25 @@
         <v>40</v>
       </c>
       <c r="BC4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,37 +1542,37 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
         <v>10.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1581,14 +1581,14 @@
         <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA4" t="n">
         <v>5.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1622,49 +1622,49 @@
         <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.94</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.98</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
@@ -1673,136 +1673,136 @@
         <v>6.4</v>
       </c>
       <c r="X5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AD5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AE5" t="n">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AF5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>430</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
         <v>11</v>
       </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>380</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
         <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
         <v>6.2</v>
@@ -1811,28 +1811,28 @@
         <v>5.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1876,91 +1876,91 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H6" t="n">
         <v>1.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
         <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.84</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.87</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AB6" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AG6" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
         <v>700</v>
@@ -1975,73 +1975,73 @@
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>55</v>
+        <v>4.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>80</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2074,7 +2074,7 @@
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>6.4</v>
@@ -2142,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.19</v>
@@ -2151,7 +2151,7 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1.1</v>
@@ -2163,25 +2163,25 @@
         <v>1.33</v>
       </c>
       <c r="R7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U7" t="n">
         <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y7" t="n">
         <v>65</v>
@@ -2211,10 +2211,10 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
         <v>19</v>
@@ -2226,7 +2226,7 @@
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN7" t="n">
         <v>4.1</v>
@@ -2244,103 +2244,103 @@
         <v>42</v>
       </c>
       <c r="AS7" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="n">
         <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BJ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BK7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
         <v>16</v>
       </c>
       <c r="BS7" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV7" t="n">
         <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
@@ -2405,10 +2405,10 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.48</v>
@@ -2420,52 +2420,52 @@
         <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.62</v>
       </c>
-      <c r="U8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.64</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
         <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI8" t="n">
         <v>32</v>
@@ -2492,7 +2492,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
         <v>17.5</v>
@@ -2504,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
         <v>11</v>
@@ -2531,37 +2531,37 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE8" t="n">
         <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG8" t="n">
         <v>13</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
         <v>4.9</v>
@@ -2570,31 +2570,31 @@
         <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR8" t="n">
         <v>26</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
         <v>5.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
         <v>17</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
@@ -2662,7 +2662,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
         <v>3.6</v>
@@ -2677,10 +2677,10 @@
         <v>1.89</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V9" t="n">
         <v>1.73</v>
@@ -2692,16 +2692,16 @@
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA9" t="n">
         <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
@@ -2737,7 +2737,7 @@
         <v>48</v>
       </c>
       <c r="AN9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2767,7 +2767,7 @@
         <v>16</v>
       </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
         <v>13.5</v>
@@ -2779,7 +2779,7 @@
         <v>19.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC9" t="n">
         <v>23</v>
@@ -2818,10 +2818,10 @@
         <v>7</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>8.6</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
         <v>5.9</v>
@@ -2913,34 +2913,34 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2949,13 +2949,13 @@
         <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA10" t="n">
         <v>690</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
         <v>9.800000000000001</v>
@@ -2967,16 +2967,16 @@
         <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
         <v>9.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>16.5</v>
@@ -2985,31 +2985,31 @@
         <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>310</v>
       </c>
       <c r="AN10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO10" t="n">
         <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR10" t="n">
         <v>42</v>
       </c>
       <c r="AS10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
         <v>9</v>
@@ -3036,37 +3036,37 @@
         <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE10" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
         <v>55</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI10" t="n">
         <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.4</v>
@@ -3081,38 +3081,38 @@
         <v>6.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX10" t="n">
         <v>44</v>
       </c>
-      <c r="BW10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>46</v>
-      </c>
       <c r="BY10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="CA10" t="n">
         <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
@@ -3167,148 +3167,148 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
         <v>2.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T11" t="n">
         <v>1.44</v>
       </c>
       <c r="U11" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X11" t="n">
         <v>36</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB11" t="n">
         <v>23</v>
       </c>
-      <c r="AA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>22</v>
-      </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT11" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
         <v>17</v>
       </c>
-      <c r="AU11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>18</v>
-      </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
         <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.800000000000001</v>
@@ -3320,25 +3320,25 @@
         <v>65</v>
       </c>
       <c r="BM11" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO11" t="n">
         <v>5.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR11" t="n">
         <v>25</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
@@ -3350,23 +3350,23 @@
         <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX11" t="n">
         <v>22</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BZ11" t="n">
         <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
         <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
         <v>70</v>
@@ -3463,25 +3463,25 @@
         <v>300</v>
       </c>
       <c r="AB12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
         <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
-        <v>260</v>
+        <v>480</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>260</v>
@@ -3496,7 +3496,7 @@
         <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN12" t="n">
         <v>6.6</v>
@@ -3505,34 +3505,34 @@
         <v>140</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
         <v>36</v>
       </c>
       <c r="AS12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>100</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
         <v>21</v>
@@ -3547,70 +3547,70 @@
         <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>80</v>
+        <v>17.5</v>
       </c>
       <c r="BH12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN12" t="n">
         <v>4</v>
       </c>
-      <c r="BI12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BO12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP12" t="n">
         <v>8.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.5</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.51</v>
-      </c>
       <c r="H13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
@@ -3678,7 +3678,7 @@
         <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
         <v>2.36</v>
@@ -3687,10 +3687,10 @@
         <v>1.71</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T13" t="n">
         <v>1.9</v>
@@ -3702,13 +3702,13 @@
         <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
         <v>70</v>
@@ -3735,28 +3735,28 @@
         <v>9.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK13" t="n">
         <v>15</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
         <v>6.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
         <v>18.5</v>
@@ -3765,10 +3765,10 @@
         <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT13" t="n">
         <v>8.6</v>
@@ -3780,10 +3780,10 @@
         <v>25</v>
       </c>
       <c r="AW13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY13" t="n">
         <v>9</v>
@@ -3801,19 +3801,19 @@
         <v>13.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BE13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BF13" t="n">
         <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
         <v>3.25</v>
@@ -3822,13 +3822,13 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN13" t="n">
         <v>4.1</v>
@@ -3840,41 +3840,41 @@
         <v>9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
         <v>11.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV13" t="n">
         <v>65</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX13" t="n">
         <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ13" t="n">
         <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3929,37 +3929,37 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
         <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
         <v>8.4</v>
@@ -3980,13 +3980,13 @@
         <v>9.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF14" t="n">
         <v>55</v>
       </c>
       <c r="AG14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -3995,16 +3995,16 @@
         <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AK14" t="n">
         <v>90</v>
       </c>
       <c r="AL14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AN14" t="n">
         <v>110</v>
@@ -4013,7 +4013,7 @@
         <v>9.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>7.6</v>
@@ -4037,34 +4037,34 @@
         <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BB14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BE14" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
         <v>3.65</v>
@@ -4076,31 +4076,31 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN14" t="n">
         <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BT14" t="n">
         <v>4.1</v>
@@ -4112,13 +4112,13 @@
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4159,172 +4159,172 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W15" t="n">
         <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
         <v>10.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>34</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT15" t="n">
         <v>17</v>
       </c>
-      <c r="AT15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AU15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AY15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>17.5</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>16</v>
-      </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BG15" t="n">
         <v>10</v>
       </c>
-      <c r="BC15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
         <v>8.800000000000001</v>
@@ -4348,16 +4348,16 @@
         <v>42</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR15" t="n">
         <v>48</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU15" t="n">
         <v>3.95</v>
@@ -4372,7 +4372,7 @@
         <v>26</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G16" t="n">
         <v>2.84</v>
@@ -4422,7 +4422,7 @@
         <v>2.94</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>3.25</v>
@@ -4455,58 +4455,58 @@
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.54</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AK16" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -4521,7 +4521,7 @@
         <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.800000000000001</v>
@@ -4530,10 +4530,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
@@ -4542,19 +4542,19 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
         <v>16</v>
@@ -4563,13 +4563,13 @@
         <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
         <v>6.8</v>
@@ -4584,7 +4584,7 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,7 +4596,7 @@
         <v>5.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.38</v>
@@ -4691,13 +4691,13 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
         <v>1.89</v>
@@ -4709,112 +4709,112 @@
         <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W17" t="n">
         <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z17" t="n">
         <v>11.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB17" t="n">
         <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL17" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>16</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AY17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
         <v>26</v>
       </c>
       <c r="BB17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD17" t="n">
         <v>46</v>
@@ -4823,10 +4823,10 @@
         <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="n">
         <v>3.8</v>
@@ -4838,46 +4838,46 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY17" t="n">
         <v>7.4</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G18" t="n">
         <v>1.8</v>
@@ -4930,40 +4930,40 @@
         <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
         <v>2.34</v>
@@ -4978,10 +4978,10 @@
         <v>30</v>
       </c>
       <c r="Y18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z18" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
@@ -4990,64 +4990,64 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
         <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>36</v>
@@ -5059,34 +5059,34 @@
         <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
         <v>55</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN18" t="n">
         <v>4.9</v>
@@ -5110,31 +5110,31 @@
         <v>12</v>
       </c>
       <c r="BQ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -5175,220 +5175,220 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G19" t="n">
         <v>4.1</v>
       </c>
-      <c r="G19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H19" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
         <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
         <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AB19" t="n">
         <v>500</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK19" t="n">
         <v>500</v>
       </c>
       <c r="AL19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN19" t="n">
         <v>500</v>
       </c>
-      <c r="AM19" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>600</v>
-      </c>
       <c r="AO19" t="n">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="AP19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9</v>
-      </c>
       <c r="AW19" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
       </c>
       <c r="BD19" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BE19" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
         <v>11</v>
       </c>
-      <c r="BG19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>12</v>
-      </c>
       <c r="BT19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BW19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.36</v>
@@ -5453,64 +5453,64 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
         <v>2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -5519,31 +5519,31 @@
         <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
         <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
         <v>90</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AP20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>15.5</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS20" t="n">
         <v>48</v>
@@ -5552,19 +5552,19 @@
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
@@ -5573,76 +5573,76 @@
         <v>38</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BH20" t="n">
         <v>3.9</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW20" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -5686,61 +5686,61 @@
         <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H21" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I21" t="n">
         <v>2.66</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
         <v>1.61</v>
       </c>
       <c r="R21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.56</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.52</v>
       </c>
       <c r="V21" t="n">
         <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
         <v>20</v>
@@ -5749,10 +5749,10 @@
         <v>48</v>
       </c>
       <c r="AB21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>12.5</v>
@@ -5761,7 +5761,7 @@
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
@@ -5782,31 +5782,31 @@
         <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
         <v>18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>10.5</v>
@@ -5824,70 +5824,70 @@
         <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO21" t="n">
         <v>5.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW21" t="n">
         <v>6.8</v>
@@ -5899,14 +5899,14 @@
         <v>7.8</v>
       </c>
       <c r="BZ21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA21" t="n">
         <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
         <v>1.82</v>
@@ -5952,7 +5952,7 @@
         <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.17</v>
@@ -5970,40 +5970,40 @@
         <v>4.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R22" t="n">
         <v>2.32</v>
       </c>
       <c r="S22" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="U22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="V22" t="n">
         <v>2.12</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z22" t="n">
         <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AC22" t="n">
         <v>16</v>
@@ -6012,10 +6012,10 @@
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG22" t="n">
         <v>21</v>
@@ -6027,10 +6027,10 @@
         <v>20</v>
       </c>
       <c r="AJ22" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="AK22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
@@ -6039,7 +6039,7 @@
         <v>46</v>
       </c>
       <c r="AN22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -6048,16 +6048,16 @@
         <v>29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR22" t="n">
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AU22" t="n">
         <v>12</v>
@@ -6069,55 +6069,55 @@
         <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ22" t="n">
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BF22" t="n">
         <v>12</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH22" t="n">
         <v>7</v>
       </c>
       <c r="BI22" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO22" t="n">
         <v>6.8</v>
@@ -6126,41 +6126,41 @@
         <v>24</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR22" t="n">
         <v>23</v>
       </c>
       <c r="BS22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT22" t="n">
         <v>6.4</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV22" t="n">
         <v>12</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BX22" t="n">
         <v>16</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BZ22" t="n">
         <v>8.4</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="n">
         <v>1.85</v>
@@ -6203,7 +6203,7 @@
         <v>1.89</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K23" t="n">
         <v>4.9</v>
@@ -6221,16 +6221,16 @@
         <v>1.11</v>
       </c>
       <c r="P23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
         <v>1.34</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S23" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="T23" t="n">
         <v>1.39</v>
@@ -6242,7 +6242,7 @@
         <v>2.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
@@ -6251,34 +6251,34 @@
         <v>22</v>
       </c>
       <c r="Z23" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD23" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AG23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>500</v>
@@ -6290,16 +6290,16 @@
         <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AQ23" t="n">
         <v>17</v>
@@ -6308,13 +6308,13 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AV23" t="n">
         <v>10</v>
@@ -6329,16 +6329,16 @@
         <v>15.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
         <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD23" t="n">
         <v>26</v>
@@ -6347,7 +6347,7 @@
         <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG23" t="n">
         <v>5</v>
@@ -6410,11 +6410,11 @@
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -6445,130 +6445,130 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I24" t="n">
         <v>1.58</v>
       </c>
       <c r="J24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="S24" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="U24" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="V24" t="n">
         <v>2.72</v>
       </c>
       <c r="W24" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="Y24" t="n">
         <v>17.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC24" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>14</v>
-      </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>13.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AG24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AJ24" t="n">
         <v>700</v>
       </c>
       <c r="AK24" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="n">
         <v>600</v>
       </c>
       <c r="AO24" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AP24" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>10</v>
@@ -6583,92 +6583,92 @@
         <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
-        <v>10.5</v>
+        <v>80</v>
       </c>
       <c r="BC24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BD24" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ24" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="BN24" t="n">
         <v>11</v>
       </c>
       <c r="BO24" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BW24" t="n">
         <v>6.8</v>
       </c>
       <c r="BX24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BY24" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="BZ24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I25" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="J25" t="n">
         <v>4.9</v>
@@ -6729,16 +6729,16 @@
         <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="T25" t="n">
         <v>1.37</v>
@@ -6747,121 +6747,121 @@
         <v>3.05</v>
       </c>
       <c r="V25" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
         <v>500</v>
       </c>
       <c r="Y25" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="Z25" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AB25" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AC25" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AD25" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AF25" t="n">
         <v>500</v>
       </c>
       <c r="AG25" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
         <v>500</v>
       </c>
       <c r="AK25" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AL25" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AO25" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AP25" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>50</v>
+        <v>4.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>29</v>
+        <v>6.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BH25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BI25" t="n">
         <v>5.2</v>
@@ -6870,31 +6870,31 @@
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BT25" t="n">
         <v>5.9</v>
@@ -6906,23 +6906,23 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="CA25" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -6953,196 +6953,196 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H26" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I26" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="S26" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="T26" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="U26" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="V26" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W26" t="n">
         <v>1.46</v>
       </c>
       <c r="X26" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y26" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB26" t="n">
         <v>28</v>
       </c>
-      <c r="Z26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>30</v>
-      </c>
       <c r="AC26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD26" t="n">
         <v>13</v>
       </c>
-      <c r="AD26" t="n">
-        <v>14</v>
-      </c>
       <c r="AE26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="n">
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>23</v>
       </c>
       <c r="AJ26" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM26" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AN26" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AQ26" t="n">
         <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AT26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BB26" t="n">
         <v>38</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
         <v>30</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG26" t="n">
         <v>7.8</v>
       </c>
       <c r="BH26" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
@@ -7151,13 +7151,13 @@
         <v>6.6</v>
       </c>
       <c r="BT26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW26" t="n">
         <v>6</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G27" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -7243,10 +7243,10 @@
         <v>1.57</v>
       </c>
       <c r="R27" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T27" t="n">
         <v>1.61</v>
@@ -7258,10 +7258,10 @@
         <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y27" t="n">
         <v>30</v>
@@ -7273,10 +7273,10 @@
         <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD27" t="n">
         <v>25</v>
@@ -7285,73 +7285,73 @@
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>32</v>
       </c>
       <c r="AM27" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AO27" t="n">
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV27" t="n">
+      <c r="AZ27" t="n">
         <v>15</v>
       </c>
-      <c r="AW27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
         <v>11.5</v>
@@ -7360,19 +7360,19 @@
         <v>19</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF27" t="n">
         <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>30</v>
+        <v>5.5</v>
       </c>
       <c r="BH27" t="n">
         <v>4.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.4</v>
@@ -7393,7 +7393,7 @@
         <v>3.65</v>
       </c>
       <c r="BP27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ27" t="n">
         <v>7.6</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -7461,34 +7461,34 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.25</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.26</v>
-      </c>
       <c r="H28" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="I28" t="n">
         <v>19.5</v>
       </c>
       <c r="J28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L28" t="n">
         <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
         <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
@@ -7503,7 +7503,7 @@
         <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
         <v>1.64</v>
@@ -7512,16 +7512,16 @@
         <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="X28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z28" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -7530,16 +7530,16 @@
         <v>7.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AE28" t="n">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="AF28" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
@@ -7551,76 +7551,76 @@
         <v>330</v>
       </c>
       <c r="AJ28" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AK28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN28" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>710</v>
       </c>
       <c r="AP28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX28" t="n">
         <v>6.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD28" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH28" t="n">
         <v>4.3</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-03 07:47:13</t>
+          <t>2026-07-03 10:04:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Loudoun United FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Sporting Club Jacksonville</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,142 +881,142 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,498 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Loudoun United FC</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>55</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S3" t="n">
         <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>2.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28</v>
+        <v>10.5</v>
       </c>
       <c r="X3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>11</v>
       </c>
-      <c r="AD3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>520</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>260</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD3" t="n">
         <v>50</v>
       </c>
-      <c r="AF3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="BE3" t="n">
+        <v>260</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AL3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="BK3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>950</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS3" t="n">
         <v>34</v>
       </c>
-      <c r="AS3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL3" t="n">
+      <c r="BT3" t="n">
         <v>1000</v>
       </c>
-      <c r="BM3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="BZ3" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-03 19:21:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Independiente (Ecu)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>300</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>640</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-07-03 19:21:27</t>
+          <t>2026-07-03 21:39:56</t>
         </is>
       </c>
     </row>
